--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10730</v>
+        <v>10829</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9453</v>
+        <v>9757</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9483</v>
+        <v>9518</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10783</v>
+        <v>10833</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10726</v>
+        <v>10746</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10730</v>
+        <v>10829</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9453</v>
+        <v>9757</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9483</v>
+        <v>9518</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10783</v>
+        <v>10833</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10726</v>
+        <v>10746</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10829</v>
+        <v>10927</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9757</v>
+        <v>10048</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9518</v>
+        <v>9548</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="H18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1288,11 +1288,11 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10833</v>
+        <v>10839</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>预售中</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10746</v>
+        <v>10759</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10829</v>
+        <v>10927</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9757</v>
+        <v>10048</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9518</v>
+        <v>9548</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="H18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2630,11 +2630,11 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10833</v>
+        <v>10839</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>预售中</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10746</v>
+        <v>10759</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10927</v>
+        <v>11042</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>10048</v>
+        <v>10226</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>虞山北路258号 星程酒店(长江路店)</t>
+          <t>虞山北路258号 星程酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9548</v>
+        <v>9585</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2429</v>
+        <v>2439</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1177,43 +1177,43 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1223,30 +1223,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>379</v>
+        <v>83</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1269,43 +1269,43 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10839</v>
+        <v>389</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1320,25 +1320,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10759</v>
+        <v>10857</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H20" t="b">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1361,43 +1361,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>7</v>
+        <v>10779</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1596,36 +1596,82 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>16</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>11</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1770,7 +1816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1894,7 +1940,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1940,7 +1986,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10927</v>
+        <v>11042</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1986,7 +2032,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>10048</v>
+        <v>10226</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2032,7 +2078,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2124,7 +2170,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2161,7 +2207,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>虞山北路258号 星程酒店(长江路店)</t>
+          <t>虞山北路258号 星程酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2170,7 +2216,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2216,7 +2262,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2262,7 +2308,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2354,7 +2400,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9548</v>
+        <v>9585</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2446,7 +2492,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2429</v>
+        <v>2439</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2492,7 +2538,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2519,43 +2565,43 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2565,30 +2611,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>379</v>
+        <v>83</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -2596,12 +2642,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2611,43 +2657,43 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10839</v>
+        <v>389</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2662,25 +2708,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10759</v>
+        <v>10857</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H20" t="b">
@@ -2688,12 +2734,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2703,43 +2749,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>7</v>
+        <v>10779</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2800,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2768,7 +2814,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2780,12 +2826,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2846,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2814,7 +2860,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2826,12 +2872,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2892,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2860,7 +2906,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2872,12 +2918,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2933,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2902,11 +2948,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2918,12 +2964,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2938,36 +2984,82 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>16</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>11</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,15 +467,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -487,43 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>昆山·“不是！你有病吧！”主题展（取消）</t>
+          <t>苏州.第二届THO 赤维极陵</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>绿地大道258号游站未来城2号楼 魔之塔</t>
+          <t>白塔东路60号(近平江路) 苏州书香府邸平江府</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 19:00</t>
+          <t>2024.01.28 10:00-01.28 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>269</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>304</v>
+      </c>
+      <c r="G2" t="n">
+        <v>65</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79002</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79124</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/Z7mV6VXN1701160508967.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/5AgvDWGQ1700817845950.jpeg</t>
         </is>
       </c>
     </row>
@@ -533,43 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>苏州.第二届THO 赤维极陵</t>
+          <t>【会员购严选】苏州·二次元开放式年会- I COME ACG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>白塔东路60号(近平江路) 苏州书香府邸平江府</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 21:00</t>
+          <t>2024.02.03 10:00-02.03 20:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>287</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>11304</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80426</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79002</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/5AgvDWGQ1700817845950.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IkyhIHPT1704352086775.jpeg</t>
         </is>
       </c>
     </row>
@@ -584,38 +569,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·二次元开放式年会- I COME ACG</t>
+          <t>苏州·TCD国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>苏州大道东688号 苏州国际博览中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 20:00</t>
+          <t>2024.02.03 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11042</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
+        <v>10596</v>
+      </c>
+      <c r="G4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80084</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80426</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IkyhIHPT1704352086775.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/aDe3s9MS1705479547745.jpeg</t>
         </is>
       </c>
     </row>
@@ -625,12 +605,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华</t>
+          <t>苏州·TCD国潮动漫游戏嘉年华吴磊内场</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -640,28 +620,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.04 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>10226</v>
+        <v>598</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
+          <t>已售罄</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80398</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80084</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/aDe3s9MS1705479547745.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/bHsHJ3f21704186294427.jpeg</t>
         </is>
       </c>
     </row>
@@ -671,43 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华吴磊内场</t>
+          <t>太仓·弇山夜宴</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>苏州大道东688号 苏州国际博览中心</t>
+          <t>城厢镇县府西街40号公园弄口 弇山园</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.04 09:30-02.04 17:00</t>
+          <t>2024.02.08 17:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>591</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80398</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/bHsHJ3f21704186294427.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
         </is>
       </c>
     </row>
@@ -717,43 +689,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>太仓·弇山夜宴</t>
+          <t>常熟·CDW·动漫展02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>城厢镇县府西街40号公园弄口 弇山园</t>
+          <t>常熟国际展览中心 国际展览中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.08 17:30-02.24 22:00</t>
+          <t>2024.02.14 09:00-02.15 17:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
+        <v>755</v>
+      </c>
+      <c r="G7" t="n">
+        <v>55</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
         </is>
       </c>
     </row>
@@ -768,38 +735,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>常熟·CDW·动漫展02</t>
+          <t>常熟·漫魂动漫游戏展01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>常熟国际展览中心 国际展览中心</t>
+          <t>虞山北路258号 星程酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:30</t>
+          <t>2024.02.14 09:00-02.14 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>722</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
+        <v>107</v>
+      </c>
+      <c r="G8" t="n">
+        <v>50</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
         </is>
       </c>
     </row>
@@ -814,38 +776,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>常熟·漫魂动漫游戏展01</t>
+          <t>张家港·META萌元漫展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>虞山北路258号 星程酒店</t>
+          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 21:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
         </is>
       </c>
     </row>
@@ -860,38 +817,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>张家港·META萌元漫展</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="G10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -901,43 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>30</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
+      <c r="G11" t="n">
+        <v>45</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -952,38 +899,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
+        <v>10511</v>
+      </c>
+      <c r="G12" t="n">
+        <v>60</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -998,7 +940,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1012,24 +954,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9585</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
+        <v>3242</v>
+      </c>
+      <c r="G13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,22 +995,17 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>55</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/swEzpIAK1705915874840.jpeg</t>
         </is>
@@ -1104,22 +1036,17 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2439</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
+        <v>2447</v>
+      </c>
+      <c r="G15" t="n">
+        <v>68</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
@@ -1150,22 +1077,17 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
+        <v>44</v>
+      </c>
+      <c r="G16" t="n">
+        <v>65</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
@@ -1196,22 +1118,17 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="G17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
@@ -1242,22 +1159,17 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>83</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
+        <v>94</v>
+      </c>
+      <c r="G18" t="n">
+        <v>78</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
@@ -1288,22 +1200,17 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>389</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
+        <v>405</v>
+      </c>
+      <c r="G19" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
@@ -1334,22 +1241,17 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10857</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
-        <v>1</v>
+        <v>11078</v>
+      </c>
+      <c r="G20" t="n">
+        <v>59</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
@@ -1380,22 +1282,17 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10779</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
-        <v>1</v>
+        <v>10823</v>
+      </c>
+      <c r="G21" t="n">
+        <v>65</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
@@ -1426,22 +1323,17 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
@@ -1472,22 +1364,17 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>16</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
@@ -1518,22 +1405,17 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
@@ -1564,22 +1446,17 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
@@ -1610,22 +1487,17 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
@@ -1656,22 +1528,17 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1688,7 +1555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1727,15 +1594,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -1752,7 +1614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1791,15 +1653,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -1816,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1855,15 +1712,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -1875,43 +1727,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>昆山·“不是！你有病吧！”主题展（取消）</t>
+          <t>苏州.第二届THO 赤维极陵</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>绿地大道258号游站未来城2号楼 魔之塔</t>
+          <t>白塔东路60号(近平江路) 苏州书香府邸平江府</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 19:00</t>
+          <t>2024.01.28 10:00-01.28 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>269</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>304</v>
+      </c>
+      <c r="G2" t="n">
+        <v>65</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79002</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79124</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/Z7mV6VXN1701160508967.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/5AgvDWGQ1700817845950.jpeg</t>
         </is>
       </c>
     </row>
@@ -1921,43 +1768,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>苏州.第二届THO 赤维极陵</t>
+          <t>【会员购严选】苏州·二次元开放式年会- I COME ACG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>白塔东路60号(近平江路) 苏州书香府邸平江府</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 21:00</t>
+          <t>2024.02.03 10:00-02.03 20:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>287</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>11304</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80426</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79002</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/5AgvDWGQ1700817845950.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IkyhIHPT1704352086775.jpeg</t>
         </is>
       </c>
     </row>
@@ -1972,38 +1814,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·二次元开放式年会- I COME ACG</t>
+          <t>苏州·TCD国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>苏州大道东688号 苏州国际博览中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 20:00</t>
+          <t>2024.02.03 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11042</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
+        <v>10596</v>
+      </c>
+      <c r="G4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80084</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80426</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IkyhIHPT1704352086775.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/aDe3s9MS1705479547745.jpeg</t>
         </is>
       </c>
     </row>
@@ -2013,12 +1850,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华</t>
+          <t>苏州·TCD国潮动漫游戏嘉年华吴磊内场</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2028,28 +1865,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.04 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>10226</v>
+        <v>598</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
+          <t>已售罄</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80398</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80084</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/aDe3s9MS1705479547745.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/bHsHJ3f21704186294427.jpeg</t>
         </is>
       </c>
     </row>
@@ -2059,43 +1893,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华吴磊内场</t>
+          <t>太仓·弇山夜宴</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>苏州大道东688号 苏州国际博览中心</t>
+          <t>城厢镇县府西街40号公园弄口 弇山园</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.04 09:30-02.04 17:00</t>
+          <t>2024.02.08 17:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>591</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80398</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/bHsHJ3f21704186294427.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
         </is>
       </c>
     </row>
@@ -2105,43 +1934,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>太仓·弇山夜宴</t>
+          <t>常熟·CDW·动漫展02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>城厢镇县府西街40号公园弄口 弇山园</t>
+          <t>常熟国际展览中心 国际展览中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.08 17:30-02.24 22:00</t>
+          <t>2024.02.14 09:00-02.15 17:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
+        <v>755</v>
+      </c>
+      <c r="G7" t="n">
+        <v>55</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
         </is>
       </c>
     </row>
@@ -2156,38 +1980,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>常熟·CDW·动漫展02</t>
+          <t>常熟·漫魂动漫游戏展01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>常熟国际展览中心 国际展览中心</t>
+          <t>虞山北路258号 星程酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:30</t>
+          <t>2024.02.14 09:00-02.14 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>722</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
+        <v>107</v>
+      </c>
+      <c r="G8" t="n">
+        <v>50</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
         </is>
       </c>
     </row>
@@ -2202,38 +2021,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>常熟·漫魂动漫游戏展01</t>
+          <t>张家港·META萌元漫展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>虞山北路258号 星程酒店</t>
+          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 21:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
         </is>
       </c>
     </row>
@@ -2248,38 +2062,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>张家港·META萌元漫展</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="G10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -2289,43 +2098,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>30</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
+      <c r="G11" t="n">
+        <v>45</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -2340,38 +2144,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
+        <v>10511</v>
+      </c>
+      <c r="G12" t="n">
+        <v>60</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2185,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2400,24 +2199,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9585</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
+        <v>3242</v>
+      </c>
+      <c r="G13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -2446,22 +2240,17 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>55</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/swEzpIAK1705915874840.jpeg</t>
         </is>
@@ -2492,22 +2281,17 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2439</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
+        <v>2447</v>
+      </c>
+      <c r="G15" t="n">
+        <v>68</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
@@ -2538,22 +2322,17 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
+        <v>44</v>
+      </c>
+      <c r="G16" t="n">
+        <v>65</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
@@ -2584,22 +2363,17 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="G17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
@@ -2630,22 +2404,17 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>83</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
+        <v>94</v>
+      </c>
+      <c r="G18" t="n">
+        <v>78</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
@@ -2676,22 +2445,17 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>389</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
+        <v>405</v>
+      </c>
+      <c r="G19" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
@@ -2722,22 +2486,17 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10857</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
-        <v>1</v>
+        <v>11078</v>
+      </c>
+      <c r="G20" t="n">
+        <v>59</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
@@ -2768,22 +2527,17 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10779</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
-        <v>1</v>
+        <v>10823</v>
+      </c>
+      <c r="G21" t="n">
+        <v>65</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
@@ -2814,22 +2568,17 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
@@ -2860,22 +2609,17 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>16</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
@@ -2906,22 +2650,17 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
@@ -2952,22 +2691,17 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
@@ -2998,22 +2732,17 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
@@ -3044,22 +2773,17 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,10 +501,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>304</v>
-      </c>
-      <c r="G2" t="n">
-        <v>65</v>
+        <v>305</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11304</v>
+        <v>11371</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
@@ -583,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10596</v>
+        <v>10707</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -667,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>39.9</v>
@@ -708,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -749,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G8" t="n">
         <v>50</v>
@@ -790,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
         <v>20</v>
@@ -831,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -872,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
         <v>45</v>
@@ -913,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10511</v>
+        <v>10544</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -954,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3242</v>
+        <v>3353</v>
       </c>
       <c r="G13" t="n">
         <v>25</v>
@@ -995,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -1118,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G18" t="n">
         <v>78</v>
@@ -1200,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="G19" t="n">
         <v>48.3</v>
@@ -1241,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11078</v>
+        <v>11088</v>
       </c>
       <c r="G20" t="n">
         <v>59</v>
@@ -1282,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10823</v>
+        <v>10837</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -1323,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1364,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1487,7 +1489,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -1746,10 +1748,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>304</v>
-      </c>
-      <c r="G2" t="n">
-        <v>65</v>
+        <v>305</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1787,7 +1791,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11304</v>
+        <v>11371</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
@@ -1828,7 +1832,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10596</v>
+        <v>10707</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1869,7 +1873,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1912,7 +1916,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>39.9</v>
@@ -1953,7 +1957,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1994,7 +1998,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G8" t="n">
         <v>50</v>
@@ -2035,7 +2039,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
         <v>20</v>
@@ -2076,7 +2080,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -2117,7 +2121,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
         <v>45</v>
@@ -2158,7 +2162,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10511</v>
+        <v>10544</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -2199,7 +2203,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3242</v>
+        <v>3354</v>
       </c>
       <c r="G13" t="n">
         <v>25</v>
@@ -2240,7 +2244,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -2363,7 +2367,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2404,7 +2408,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G18" t="n">
         <v>78</v>
@@ -2445,7 +2449,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="G19" t="n">
         <v>48.3</v>
@@ -2486,7 +2490,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11078</v>
+        <v>11088</v>
       </c>
       <c r="G20" t="n">
         <v>59</v>
@@ -2527,7 +2531,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10823</v>
+        <v>10837</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -2568,7 +2572,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -2609,7 +2613,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -2732,7 +2736,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,40 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>苏州.第二届THO 赤维极陵</t>
+          <t>【会员购严选】苏州·二次元开放式年会- I COME ACG</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>白塔东路60号(近平江路) 苏州书香府邸平江府</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 21:00</t>
+          <t>2024.02.03 10:00-02.03 20:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>305</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>11408</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79002</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80426</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/5AgvDWGQ1700817845950.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IkyhIHPT1704352086775.jpeg</t>
         </is>
       </c>
     </row>
@@ -530,33 +528,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·二次元开放式年会- I COME ACG</t>
+          <t>苏州·TCD国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>苏州大道东688号 苏州国际博览中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 20:00</t>
+          <t>2024.02.03 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11371</v>
+        <v>10768</v>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80426</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80084</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IkyhIHPT1704352086775.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/aDe3s9MS1705479547745.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,12 +564,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华</t>
+          <t>苏州·TCD国潮动漫游戏嘉年华吴磊内场</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -581,23 +579,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.04 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10707</v>
-      </c>
-      <c r="G4" t="n">
-        <v>60</v>
+        <v>600</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80084</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80398</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/aDe3s9MS1705479547745.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/bHsHJ3f21704186294427.jpeg</t>
         </is>
       </c>
     </row>
@@ -607,40 +607,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华吴磊内场</t>
+          <t>太仓·弇山夜宴</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>苏州大道东688号 苏州国际博览中心</t>
+          <t>城厢镇县府西街40号公园弄口 弇山园</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.04 09:30-02.04 17:00</t>
+          <t>2024.02.08 17:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>599</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>39.9</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/bHsHJ3f21704186294427.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
         </is>
       </c>
     </row>
@@ -650,38 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>太仓·弇山夜宴</t>
+          <t>常熟·CDW·动漫展02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>城厢镇县府西街40号公园弄口 弇山园</t>
+          <t>常熟国际展览中心 国际展览中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.08 17:30-02.24 22:00</t>
+          <t>2024.02.14 09:00-02.15 17:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>979</v>
       </c>
       <c r="G6" t="n">
-        <v>39.9</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
         </is>
       </c>
     </row>
@@ -696,33 +694,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>常熟·CDW·动漫展02</t>
+          <t>常熟·漫魂动漫游戏展01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>常熟国际展览中心 国际展览中心</t>
+          <t>虞山北路258号 星程酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:30</t>
+          <t>2024.02.14 09:00-02.14 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>770</v>
+        <v>114</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
         </is>
       </c>
     </row>
@@ -737,33 +735,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>常熟·漫魂动漫游戏展01</t>
+          <t>张家港·META萌元漫展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>虞山北路258号 星程酒店</t>
+          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 21:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
         </is>
       </c>
     </row>
@@ -778,33 +776,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>张家港·META萌元漫展</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -814,38 +812,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -860,33 +858,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>10571</v>
       </c>
       <c r="G11" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -901,7 +899,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -915,19 +913,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10544</v>
+        <v>4079</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -937,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3353</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/swEzpIAK1705915874840.jpeg</t>
         </is>
       </c>
     </row>
@@ -983,12 +981,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -997,19 +995,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>2450</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/swEzpIAK1705915874840.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -1019,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>木渎金山南路288号 苏州国际影视娱乐城</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2447</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -1060,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>木渎金山南路288号 苏州国际影视娱乐城</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1101,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1142,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>98</v>
+        <v>416</v>
       </c>
       <c r="G18" t="n">
-        <v>78</v>
+        <v>48.3</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1183,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>412</v>
+        <v>11091</v>
       </c>
       <c r="G19" t="n">
-        <v>48.3</v>
+        <v>59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1229,33 +1227,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11088</v>
+        <v>10845</v>
       </c>
       <c r="G20" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1265,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10837</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1309,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1325,19 +1323,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1350,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1366,19 +1364,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1391,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1407,19 +1405,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1427,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1444,23 +1442,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1473,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1489,58 +1487,17 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>12</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1675,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1729,40 +1686,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>苏州.第二届THO 赤维极陵</t>
+          <t>【会员购严选】苏州·二次元开放式年会- I COME ACG</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>白塔东路60号(近平江路) 苏州书香府邸平江府</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 21:00</t>
+          <t>2024.02.03 10:00-02.03 20:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>305</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>11408</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79002</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80426</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/5AgvDWGQ1700817845950.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IkyhIHPT1704352086775.jpeg</t>
         </is>
       </c>
     </row>
@@ -1777,33 +1732,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·二次元开放式年会- I COME ACG</t>
+          <t>苏州·TCD国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>苏州大道东688号 苏州国际博览中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 20:00</t>
+          <t>2024.02.03 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11371</v>
+        <v>10769</v>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80426</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80084</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IkyhIHPT1704352086775.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/aDe3s9MS1705479547745.jpeg</t>
         </is>
       </c>
     </row>
@@ -1813,12 +1768,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华</t>
+          <t>苏州·TCD国潮动漫游戏嘉年华吴磊内场</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1828,23 +1783,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.04 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10707</v>
-      </c>
-      <c r="G4" t="n">
-        <v>60</v>
+        <v>600</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80084</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80398</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/aDe3s9MS1705479547745.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/bHsHJ3f21704186294427.jpeg</t>
         </is>
       </c>
     </row>
@@ -1854,40 +1811,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华吴磊内场</t>
+          <t>太仓·弇山夜宴</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>苏州大道东688号 苏州国际博览中心</t>
+          <t>城厢镇县府西街40号公园弄口 弇山园</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.04 09:30-02.04 17:00</t>
+          <t>2024.02.08 17:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>599</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>39.9</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/bHsHJ3f21704186294427.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
         </is>
       </c>
     </row>
@@ -1897,38 +1852,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>太仓·弇山夜宴</t>
+          <t>常熟·CDW·动漫展02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>城厢镇县府西街40号公园弄口 弇山园</t>
+          <t>常熟国际展览中心 国际展览中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.08 17:30-02.24 22:00</t>
+          <t>2024.02.14 09:00-02.15 17:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>979</v>
       </c>
       <c r="G6" t="n">
-        <v>39.9</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
         </is>
       </c>
     </row>
@@ -1943,33 +1898,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>常熟·CDW·动漫展02</t>
+          <t>常熟·漫魂动漫游戏展01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>常熟国际展览中心 国际展览中心</t>
+          <t>虞山北路258号 星程酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:30</t>
+          <t>2024.02.14 09:00-02.14 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>770</v>
+        <v>114</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
         </is>
       </c>
     </row>
@@ -1984,33 +1939,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>常熟·漫魂动漫游戏展01</t>
+          <t>张家港·META萌元漫展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>虞山北路258号 星程酒店</t>
+          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 21:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
         </is>
       </c>
     </row>
@@ -2025,33 +1980,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>张家港·META萌元漫展</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -2061,38 +2016,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -2107,33 +2062,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>10571</v>
       </c>
       <c r="G11" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2103,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2162,19 +2117,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10544</v>
+        <v>4079</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -2184,38 +2139,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3354</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/swEzpIAK1705915874840.jpeg</t>
         </is>
       </c>
     </row>
@@ -2230,12 +2185,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2244,19 +2199,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>2450</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/swEzpIAK1705915874840.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -2266,38 +2221,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>木渎金山南路288号 苏州国际影视娱乐城</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2447</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -2307,38 +2262,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>木渎金山南路288号 苏州国际影视娱乐城</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2348,38 +2303,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2389,38 +2344,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>98</v>
+        <v>416</v>
       </c>
       <c r="G18" t="n">
-        <v>78</v>
+        <v>48.3</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2430,38 +2385,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>412</v>
+        <v>11091</v>
       </c>
       <c r="G19" t="n">
-        <v>48.3</v>
+        <v>59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2476,33 +2431,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11088</v>
+        <v>10845</v>
       </c>
       <c r="G20" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2512,38 +2467,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10837</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2513,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2572,19 +2527,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2554,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2613,19 +2568,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2595,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2654,19 +2609,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2631,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2691,23 +2646,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2677,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2736,58 +2691,17 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>12</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11408</v>
+        <v>11470</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10768</v>
+        <v>10913</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>39.9</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10571</v>
+        <v>10607</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4079</v>
+        <v>4098</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/swEzpIAK1705915874840.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2450</v>
+        <v>2453</v>
       </c>
       <c r="G14" t="n">
         <v>68</v>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>木渎金山南路288号 苏州国际影视娱乐城</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G17" t="n">
         <v>78</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="G18" t="n">
         <v>48.3</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11091</v>
+        <v>11098</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10845</v>
+        <v>10858</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11408</v>
+        <v>11470</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10769</v>
+        <v>10914</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>39.9</v>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10571</v>
+        <v>10607</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4079</v>
+        <v>4098</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/swEzpIAK1705915874840.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2450</v>
+        <v>2453</v>
       </c>
       <c r="G14" t="n">
         <v>68</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>木渎金山南路288号 苏州国际影视娱乐城</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G17" t="n">
         <v>78</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="G18" t="n">
         <v>48.3</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11091</v>
+        <v>11098</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10845</v>
+        <v>10858</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11470</v>
+        <v>11499</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10913</v>
+        <v>10963</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>39.9</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>985</v>
+        <v>994</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10607</v>
+        <v>10623</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4098</v>
+        <v>4107</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
         <v>45</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="G14" t="n">
         <v>68</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G17" t="n">
         <v>78</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G18" t="n">
         <v>48.3</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11098</v>
+        <v>11101</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10858</v>
+        <v>10864</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11470</v>
+        <v>11499</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10914</v>
+        <v>10963</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>39.9</v>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>985</v>
+        <v>994</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10607</v>
+        <v>10623</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4098</v>
+        <v>4107</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
         <v>45</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="G14" t="n">
         <v>68</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G17" t="n">
         <v>78</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G18" t="n">
         <v>48.3</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11098</v>
+        <v>11101</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10858</v>
+        <v>10864</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11499</v>
+        <v>11561</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10963</v>
+        <v>11077</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>994</v>
+        <v>1003</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10623</v>
+        <v>10663</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4107</v>
+        <v>4115</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -935,38 +935,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" t="n">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -981,12 +983,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -995,19 +997,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2455</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1019,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>2457</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1060,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1101,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="G17" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1142,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>423</v>
+        <v>116</v>
       </c>
       <c r="G18" t="n">
-        <v>48.3</v>
+        <v>78</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1183,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11101</v>
+        <v>425</v>
       </c>
       <c r="G19" t="n">
-        <v>59</v>
+        <v>48.3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1227,33 +1229,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10864</v>
+        <v>11105</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1265,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>10869</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1311,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1323,19 +1325,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1352,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1364,19 +1366,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1393,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1405,19 +1407,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1429,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1442,23 +1444,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1475,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1487,17 +1489,58 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>13</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1632,7 +1675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1705,7 +1748,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11499</v>
+        <v>11561</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -1746,7 +1789,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10963</v>
+        <v>11077</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -1871,7 +1914,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>994</v>
+        <v>1003</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1912,7 +1955,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -1953,7 +1996,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -1994,7 +2037,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -2035,7 +2078,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -2076,7 +2119,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10623</v>
+        <v>10663</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2117,7 +2160,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4107</v>
+        <v>4115</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -2139,38 +2182,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" t="n">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2230,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2199,19 +2244,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2455</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -2221,38 +2266,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>2457</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -2262,38 +2307,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -2303,38 +2348,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="G17" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2344,38 +2389,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>423</v>
+        <v>116</v>
       </c>
       <c r="G18" t="n">
-        <v>48.3</v>
+        <v>78</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2385,38 +2430,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11101</v>
+        <v>425</v>
       </c>
       <c r="G19" t="n">
-        <v>59</v>
+        <v>48.3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2431,33 +2476,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10864</v>
+        <v>11105</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2467,38 +2512,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>10869</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2558,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2527,19 +2572,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2599,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2568,19 +2613,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2640,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2609,19 +2654,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2631,12 +2676,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2646,23 +2691,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2722,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2691,17 +2736,58 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>13</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11561</v>
+        <v>11591</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11077</v>
+        <v>11133</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10663</v>
+        <v>10674</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4115</v>
+        <v>4124</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2457</v>
+        <v>2460</v>
       </c>
       <c r="G15" t="n">
         <v>68</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G18" t="n">
         <v>78</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="G19" t="n">
         <v>48.3</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11105</v>
+        <v>11112</v>
       </c>
       <c r="G20" t="n">
         <v>59</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10869</v>
+        <v>10881</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11561</v>
+        <v>11591</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11077</v>
+        <v>11133</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10663</v>
+        <v>10674</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4115</v>
+        <v>4124</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2457</v>
+        <v>2460</v>
       </c>
       <c r="G15" t="n">
         <v>68</v>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G18" t="n">
         <v>78</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="G19" t="n">
         <v>48.3</v>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11105</v>
+        <v>11112</v>
       </c>
       <c r="G20" t="n">
         <v>59</v>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10869</v>
+        <v>10881</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11591</v>
+        <v>11642</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11133</v>
+        <v>11212</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10674</v>
+        <v>10701</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4124</v>
+        <v>4138</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -954,12 +954,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="G13" t="n">
+        <v>30</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -978,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1022,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1038,19 +1036,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2460</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1060,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>48</v>
+        <v>2461</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -1101,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>1050</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -1142,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="G18" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1183,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>432</v>
+        <v>121</v>
       </c>
       <c r="G19" t="n">
-        <v>48.3</v>
+        <v>78</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1224,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11112</v>
+        <v>438</v>
       </c>
       <c r="G20" t="n">
-        <v>59</v>
+        <v>48.3</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1270,33 +1268,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10881</v>
+        <v>11122</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1306,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>10889</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1350,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1366,19 +1364,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1391,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1407,19 +1405,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1432,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1448,19 +1446,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1468,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1485,23 +1483,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1514,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1530,17 +1528,58 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>13</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1675,7 +1714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1748,7 +1787,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11591</v>
+        <v>11642</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -1789,7 +1828,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11133</v>
+        <v>11212</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -1830,7 +1869,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1914,7 +1953,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1955,7 +1994,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -1996,7 +2035,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -2037,7 +2076,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -2078,7 +2117,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -2119,7 +2158,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10674</v>
+        <v>10701</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2160,7 +2199,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4124</v>
+        <v>4138</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -2201,12 +2240,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="G13" t="n">
+        <v>30</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2225,38 +2262,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2308,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2285,19 +2322,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2460</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -2307,38 +2344,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>48</v>
+        <v>2461</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -2348,38 +2385,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>1050</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -2389,38 +2426,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="G18" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2430,38 +2467,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>432</v>
+        <v>121</v>
       </c>
       <c r="G19" t="n">
-        <v>48.3</v>
+        <v>78</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2471,38 +2508,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11112</v>
+        <v>438</v>
       </c>
       <c r="G20" t="n">
-        <v>59</v>
+        <v>48.3</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2517,33 +2554,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10881</v>
+        <v>11122</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2553,38 +2590,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>10889</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2636,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2613,19 +2650,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2677,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2654,19 +2691,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2718,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2695,19 +2732,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2717,12 +2754,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2732,23 +2769,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2800,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2777,17 +2814,58 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>13</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11642</v>
+        <v>11665</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11212</v>
+        <v>11249</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10701</v>
+        <v>10719</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4138</v>
+        <v>4145</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
         <v>20</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
         <v>45</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="G20" t="n">
-        <v>48.3</v>
+        <v>49.9</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11122</v>
+        <v>11129</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10889</v>
+        <v>10908</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11642</v>
+        <v>11666</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11212</v>
+        <v>11249</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10701</v>
+        <v>10719</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4138</v>
+        <v>4145</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
         <v>20</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
         <v>45</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="G20" t="n">
-        <v>48.3</v>
+        <v>49.9</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11122</v>
+        <v>11129</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10889</v>
+        <v>10908</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11665</v>
+        <v>11706</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11249</v>
+        <v>11327</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10719</v>
+        <v>10749</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4145</v>
+        <v>4159</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
         <v>20</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
         <v>45</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2461</v>
+        <v>2466</v>
       </c>
       <c r="G16" t="n">
         <v>68</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11129</v>
+        <v>11137</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10908</v>
+        <v>10920</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11666</v>
+        <v>11706</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11249</v>
+        <v>11328</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10719</v>
+        <v>10749</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4145</v>
+        <v>4159</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
         <v>20</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
         <v>45</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2461</v>
+        <v>2466</v>
       </c>
       <c r="G16" t="n">
         <v>68</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11129</v>
+        <v>11137</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10908</v>
+        <v>10920</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11706</v>
+        <v>11732</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11327</v>
+        <v>11362</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
         <v>39.9</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10749</v>
+        <v>10774</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4159</v>
+        <v>4165</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2466</v>
+        <v>2469</v>
       </c>
       <c r="G16" t="n">
         <v>68</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11137</v>
+        <v>11144</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10920</v>
+        <v>10928</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11706</v>
+        <v>11732</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11328</v>
+        <v>11362</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
         <v>39.9</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10749</v>
+        <v>10774</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4159</v>
+        <v>4165</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2466</v>
+        <v>2469</v>
       </c>
       <c r="G16" t="n">
         <v>68</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11137</v>
+        <v>11144</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10920</v>
+        <v>10928</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11732</v>
+        <v>11786</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11362</v>
+        <v>11467</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10774</v>
+        <v>10817</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4165</v>
+        <v>4180</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
         <v>20</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="G16" t="n">
         <v>68</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1181,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>78</v>
+        <v>29.9</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -1222,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>451</v>
+        <v>131</v>
       </c>
       <c r="G20" t="n">
-        <v>49.9</v>
+        <v>78</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11144</v>
+        <v>454</v>
       </c>
       <c r="G21" t="n">
-        <v>59</v>
+        <v>49.9</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1309,33 +1309,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10928</v>
+        <v>11153</v>
       </c>
       <c r="G22" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1345,38 +1345,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>10940</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1405,19 +1405,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1446,19 +1446,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1487,19 +1487,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1524,23 +1524,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1569,17 +1569,58 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>15</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1714,7 +1755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1787,7 +1828,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11732</v>
+        <v>11786</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -1828,7 +1869,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11362</v>
+        <v>11467</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -1869,7 +1910,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1953,7 +1994,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1994,7 +2035,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -2035,7 +2076,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -2076,7 +2117,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -2117,7 +2158,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
         <v>45</v>
@@ -2158,7 +2199,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10774</v>
+        <v>10817</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2199,7 +2240,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4165</v>
+        <v>4180</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -2240,7 +2281,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -2281,7 +2322,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
         <v>20</v>
@@ -2363,7 +2404,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="G16" t="n">
         <v>68</v>
@@ -2404,7 +2445,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -2445,7 +2486,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -2467,38 +2508,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>78</v>
+        <v>29.9</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -2508,38 +2549,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>451</v>
+        <v>131</v>
       </c>
       <c r="G20" t="n">
-        <v>49.9</v>
+        <v>78</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2549,38 +2590,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11144</v>
+        <v>454</v>
       </c>
       <c r="G21" t="n">
-        <v>59</v>
+        <v>49.9</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2595,33 +2636,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10928</v>
+        <v>11153</v>
       </c>
       <c r="G22" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2631,38 +2672,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>10940</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2718,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2691,19 +2732,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2759,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2732,19 +2773,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2800,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2773,19 +2814,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2795,12 +2836,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2810,23 +2851,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2882,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2855,17 +2896,58 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>15</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11786</v>
+        <v>11809</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11467</v>
+        <v>11532</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10817</v>
+        <v>10848</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4180</v>
+        <v>4188</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
         <v>20</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="G16" t="n">
         <v>68</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
         <v>29.9</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G21" t="n">
         <v>49.9</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11153</v>
+        <v>11157</v>
       </c>
       <c r="G22" t="n">
         <v>59</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>10940</v>
+        <v>10953</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11786</v>
+        <v>11809</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11467</v>
+        <v>11532</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10817</v>
+        <v>10848</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4180</v>
+        <v>4188</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
         <v>20</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="G16" t="n">
         <v>68</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
         <v>29.9</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G21" t="n">
         <v>49.9</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11153</v>
+        <v>11157</v>
       </c>
       <c r="G22" t="n">
         <v>59</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>10940</v>
+        <v>10953</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,33 +487,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·二次元开放式年会- I COME ACG</t>
+          <t>苏州·TCD国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>苏州大道东688号 苏州国际博览中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 20:00</t>
+          <t>2024.02.03 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11809</v>
+        <v>11602</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80426</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80084</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IkyhIHPT1704352086775.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/aDe3s9MS1705479547745.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,12 +523,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华</t>
+          <t>苏州·TCD国潮动漫游戏嘉年华吴磊内场</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -538,23 +538,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.04 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11532</v>
-      </c>
-      <c r="G3" t="n">
-        <v>109</v>
+        <v>612</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80084</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80398</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/aDe3s9MS1705479547745.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/bHsHJ3f21704186294427.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,40 +566,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华吴磊内场</t>
+          <t>太仓·弇山夜宴</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>苏州大道东688号 苏州国际博览中心</t>
+          <t>城厢镇县府西街40号公园弄口 弇山园</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.04 09:30-02.04 17:00</t>
+          <t>2024.02.08 17:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>611</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/bHsHJ3f21704186294427.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
         </is>
       </c>
     </row>
@@ -607,38 +607,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>太仓·弇山夜宴</t>
+          <t>常熟·CDW·动漫展02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>城厢镇县府西街40号公园弄口 弇山园</t>
+          <t>常熟国际展览中心 国际展览中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.08 17:30-02.24 22:00</t>
+          <t>2024.02.14 09:00-02.15 17:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>1053</v>
       </c>
       <c r="G5" t="n">
-        <v>39.9</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
         </is>
       </c>
     </row>
@@ -653,33 +653,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>常熟·CDW·动漫展02</t>
+          <t>常熟·漫魂动漫游戏展01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>常熟国际展览中心 国际展览中心</t>
+          <t>虞山北路258号 星程酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:30</t>
+          <t>2024.02.14 09:00-02.14 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1040</v>
+        <v>123</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
         </is>
       </c>
     </row>
@@ -694,33 +694,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>常熟·漫魂动漫游戏展01</t>
+          <t>张家港·META萌元漫展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>虞山北路258号 星程酒店</t>
+          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 21:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
         </is>
       </c>
     </row>
@@ -735,33 +735,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>张家港·META萌元漫展</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -817,33 +817,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>10927</v>
       </c>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10848</v>
+        <v>4217</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4188</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -940,33 +940,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>15</v>
+      </c>
+      <c r="G13" t="n">
         <v>20</v>
       </c>
-      <c r="G13" t="n">
-        <v>30</v>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1036,19 +1036,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>2479</v>
       </c>
       <c r="G15" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2473</v>
+        <v>1057</v>
       </c>
       <c r="G16" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1056</v>
+        <v>61</v>
       </c>
       <c r="G17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>29.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="G19" t="n">
-        <v>29.9</v>
+        <v>78</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1222,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>134</v>
+        <v>459</v>
       </c>
       <c r="G20" t="n">
-        <v>78</v>
+        <v>49.9</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>456</v>
+        <v>11168</v>
       </c>
       <c r="G21" t="n">
-        <v>49.9</v>
+        <v>59</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1309,33 +1309,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11157</v>
+        <v>10983</v>
       </c>
       <c r="G22" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1345,38 +1345,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>10953</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1405,19 +1405,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1446,19 +1446,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1487,19 +1487,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1524,23 +1524,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1569,58 +1569,17 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>15</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1755,7 +1714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1814,33 +1773,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·二次元开放式年会- I COME ACG</t>
+          <t>苏州·TCD国潮动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>苏州大道东688号 苏州国际博览中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 20:00</t>
+          <t>2024.02.03 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11809</v>
+        <v>11602</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80426</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80084</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IkyhIHPT1704352086775.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/aDe3s9MS1705479547745.jpeg</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1809,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华</t>
+          <t>苏州·TCD国潮动漫游戏嘉年华吴磊内场</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1865,23 +1824,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.04 09:30-02.04 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11532</v>
-      </c>
-      <c r="G3" t="n">
-        <v>109</v>
+        <v>612</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80084</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80398</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/aDe3s9MS1705479547745.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/bHsHJ3f21704186294427.jpeg</t>
         </is>
       </c>
     </row>
@@ -1891,40 +1852,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华吴磊内场</t>
+          <t>太仓·弇山夜宴</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>苏州大道东688号 苏州国际博览中心</t>
+          <t>城厢镇县府西街40号公园弄口 弇山园</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.04 09:30-02.04 17:00</t>
+          <t>2024.02.08 17:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>611</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/bHsHJ3f21704186294427.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
         </is>
       </c>
     </row>
@@ -1934,38 +1893,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>太仓·弇山夜宴</t>
+          <t>常熟·CDW·动漫展02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>城厢镇县府西街40号公园弄口 弇山园</t>
+          <t>常熟国际展览中心 国际展览中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.08 17:30-02.24 22:00</t>
+          <t>2024.02.14 09:00-02.15 17:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>1053</v>
       </c>
       <c r="G5" t="n">
-        <v>39.9</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
         </is>
       </c>
     </row>
@@ -1980,33 +1939,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>常熟·CDW·动漫展02</t>
+          <t>常熟·漫魂动漫游戏展01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>常熟国际展览中心 国际展览中心</t>
+          <t>虞山北路258号 星程酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:30</t>
+          <t>2024.02.14 09:00-02.14 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1040</v>
+        <v>123</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
         </is>
       </c>
     </row>
@@ -2021,33 +1980,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>常熟·漫魂动漫游戏展01</t>
+          <t>张家港·META萌元漫展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>虞山北路258号 星程酒店</t>
+          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 21:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
         </is>
       </c>
     </row>
@@ -2062,33 +2021,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>张家港·META萌元漫展</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -2098,38 +2057,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -2144,33 +2103,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>10927</v>
       </c>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2144,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2199,19 +2158,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10848</v>
+        <v>4217</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -2221,38 +2180,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4188</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -2267,33 +2226,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>15</v>
+      </c>
+      <c r="G13" t="n">
         <v>20</v>
       </c>
-      <c r="G13" t="n">
-        <v>30</v>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -2303,38 +2262,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -2349,12 +2308,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2363,19 +2322,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>2479</v>
       </c>
       <c r="G15" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -2385,38 +2344,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2473</v>
+        <v>1057</v>
       </c>
       <c r="G16" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -2426,38 +2385,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1056</v>
+        <v>61</v>
       </c>
       <c r="G17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2467,38 +2426,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>29.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -2508,38 +2467,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="G19" t="n">
-        <v>29.9</v>
+        <v>78</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2549,38 +2508,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>134</v>
+        <v>459</v>
       </c>
       <c r="G20" t="n">
-        <v>78</v>
+        <v>49.9</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2590,38 +2549,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>456</v>
+        <v>11168</v>
       </c>
       <c r="G21" t="n">
-        <v>49.9</v>
+        <v>59</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2636,33 +2595,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11157</v>
+        <v>10983</v>
       </c>
       <c r="G22" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2672,38 +2631,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>10953</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2677,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2732,19 +2691,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2718,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2773,19 +2732,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2759,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2814,19 +2773,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2836,12 +2795,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2851,23 +2810,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2841,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2896,58 +2855,17 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>15</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11602</v>
+        <v>11621</v>
       </c>
       <c r="G2" t="n">
         <v>109</v>
@@ -546,7 +546,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
         <v>20</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
         <v>45</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10927</v>
+        <v>10990</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4217</v>
+        <v>4230</v>
       </c>
       <c r="G11" t="n">
         <v>25</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G13" t="n">
         <v>20</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2479</v>
+        <v>2483</v>
       </c>
       <c r="G15" t="n">
         <v>68</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
         <v>29.9</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11168</v>
+        <v>11180</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10983</v>
+        <v>10999</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11602</v>
+        <v>11621</v>
       </c>
       <c r="G2" t="n">
         <v>109</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
         <v>20</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
         <v>45</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10927</v>
+        <v>10990</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4217</v>
+        <v>4230</v>
       </c>
       <c r="G11" t="n">
         <v>25</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G13" t="n">
         <v>20</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2479</v>
+        <v>2483</v>
       </c>
       <c r="G15" t="n">
         <v>68</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
         <v>29.9</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11168</v>
+        <v>11180</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10983</v>
+        <v>10999</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华</t>
+          <t>太仓·弇山夜宴</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>苏州大道东688号 苏州国际博览中心</t>
+          <t>城厢镇县府西街40号公园弄口 弇山园</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.08 17:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11621</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>109</v>
+        <v>39.9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80084</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/aDe3s9MS1705479547745.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,40 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华吴磊内场</t>
+          <t>常熟·CDW·动漫展02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>苏州大道东688号 苏州国际博览中心</t>
+          <t>常熟国际展览中心 国际展览中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.04 09:30-02.04 17:00</t>
+          <t>2024.02.14 09:00-02.15 17:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>612</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1070</v>
+      </c>
+      <c r="G3" t="n">
+        <v>55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/bHsHJ3f21704186294427.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>太仓·弇山夜宴</t>
+          <t>常熟·漫魂动漫游戏展01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>城厢镇县府西街40号公园弄口 弇山园</t>
+          <t>虞山北路258号 星程酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.08 17:30-02.24 22:00</t>
+          <t>2024.02.14 09:00-02.14 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="G4" t="n">
-        <v>39.9</v>
+        <v>50</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
         </is>
       </c>
     </row>
@@ -612,33 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>常熟·CDW·动漫展02</t>
+          <t>张家港·META萌元漫展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>常熟国际展览中心 国际展览中心</t>
+          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1057</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
         </is>
       </c>
     </row>
@@ -653,33 +651,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>常熟·漫魂动漫游戏展01</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>虞山北路258号 星程酒店</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 21:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -689,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>张家港·META萌元漫展</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -730,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>11089</v>
       </c>
       <c r="G8" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -776,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>4265</v>
       </c>
       <c r="G9" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -812,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10990</v>
+        <v>24</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4230</v>
+        <v>19</v>
       </c>
       <c r="G11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,38 +933,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>16</v>
+        <v>2491</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +974,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>1066</v>
       </c>
       <c r="G14" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1015,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1032,23 +1030,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2483</v>
+        <v>79</v>
       </c>
       <c r="G15" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1056,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1060</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>29.9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1097,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1138,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>476</v>
       </c>
       <c r="G18" t="n">
-        <v>29.9</v>
+        <v>49.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1179,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>147</v>
+        <v>11201</v>
       </c>
       <c r="G19" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1222,38 +1220,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>467</v>
+        <v>11033</v>
       </c>
       <c r="G20" t="n">
-        <v>49.9</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1261,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1278,23 +1276,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11180</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1304,38 +1302,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10999</v>
+        <v>35</v>
       </c>
       <c r="G22" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1348,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1364,19 +1362,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1389,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1405,19 +1403,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1425,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1442,23 +1440,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1466,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1483,103 +1481,21 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>30</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>16</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1714,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1768,38 +1684,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华</t>
+          <t>太仓·弇山夜宴</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>苏州大道东688号 苏州国际博览中心</t>
+          <t>城厢镇县府西街40号公园弄口 弇山园</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.04 17:00</t>
+          <t>2024.02.08 17:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11621</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>109</v>
+        <v>39.9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80084</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/aDe3s9MS1705479547745.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
         </is>
       </c>
     </row>
@@ -1809,40 +1725,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>苏州·TCD国潮动漫游戏嘉年华吴磊内场</t>
+          <t>常熟·CDW·动漫展02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>苏州大道东688号 苏州国际博览中心</t>
+          <t>常熟国际展览中心 国际展览中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.04 09:30-02.04 17:00</t>
+          <t>2024.02.14 09:00-02.15 17:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>612</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1070</v>
+      </c>
+      <c r="G3" t="n">
+        <v>55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80398</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/bHsHJ3f21704186294427.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
         </is>
       </c>
     </row>
@@ -1852,38 +1766,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>太仓·弇山夜宴</t>
+          <t>常熟·漫魂动漫游戏展01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>城厢镇县府西街40号公园弄口 弇山园</t>
+          <t>虞山北路258号 星程酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.08 17:30-02.24 22:00</t>
+          <t>2024.02.14 09:00-02.14 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="G4" t="n">
-        <v>39.9</v>
+        <v>50</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
         </is>
       </c>
     </row>
@@ -1898,33 +1812,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>常熟·CDW·动漫展02</t>
+          <t>张家港·META萌元漫展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>常熟国际展览中心 国际展览中心</t>
+          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:30</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1057</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
         </is>
       </c>
     </row>
@@ -1939,33 +1853,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>常熟·漫魂动漫游戏展01</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>虞山北路258号 星程酒店</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 21:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1975,38 +1889,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>张家港·META萌元漫展</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -2016,38 +1930,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>11089</v>
       </c>
       <c r="G8" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -2062,33 +1976,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>4265</v>
       </c>
       <c r="G9" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -2098,38 +2012,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10990</v>
+        <v>24</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -2139,38 +2053,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4230</v>
+        <v>19</v>
       </c>
       <c r="G11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -2180,38 +2094,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -2221,38 +2135,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>16</v>
+        <v>2491</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -2262,38 +2176,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>1066</v>
       </c>
       <c r="G14" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -2303,12 +2217,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2318,23 +2232,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2483</v>
+        <v>79</v>
       </c>
       <c r="G15" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2344,38 +2258,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1060</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>29.9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -2385,38 +2299,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2426,38 +2340,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>476</v>
       </c>
       <c r="G18" t="n">
-        <v>29.9</v>
+        <v>49.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2467,38 +2381,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>147</v>
+        <v>11201</v>
       </c>
       <c r="G19" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2508,38 +2422,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>467</v>
+        <v>11033</v>
       </c>
       <c r="G20" t="n">
-        <v>49.9</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2463,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2564,23 +2478,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11180</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2590,38 +2504,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10999</v>
+        <v>35</v>
       </c>
       <c r="G22" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2550,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2650,19 +2564,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2591,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2691,19 +2605,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2627,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2728,23 +2642,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2668,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2769,103 +2683,21 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>30</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>16</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
         <v>45</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11089</v>
+        <v>11144</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4265</v>
+        <v>4276</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2491</v>
+        <v>2496</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G17" t="n">
         <v>78</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="G18" t="n">
         <v>49.9</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11201</v>
+        <v>11220</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11033</v>
+        <v>11064</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
         <v>45</v>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11089</v>
+        <v>11144</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4265</v>
+        <v>4276</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2491</v>
+        <v>2496</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G17" t="n">
         <v>78</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="G18" t="n">
         <v>49.9</v>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11201</v>
+        <v>11220</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11033</v>
+        <v>11064</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1075</v>
+        <v>1093</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,10 +583,12 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>126</v>
-      </c>
-      <c r="G4" t="n">
-        <v>50</v>
+        <v>125</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -624,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -665,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
         <v>49</v>
@@ -706,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G7" t="n">
         <v>45</v>
@@ -747,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11144</v>
+        <v>11231</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4276</v>
+        <v>4290</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -829,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -870,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -911,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -952,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2496</v>
+        <v>2501</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -993,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1034,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -1116,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G17" t="n">
         <v>78</v>
@@ -1157,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="G18" t="n">
         <v>49.9</v>
@@ -1198,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11220</v>
+        <v>11240</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -1239,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11064</v>
+        <v>11090</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -1444,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1703,7 +1705,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -1744,7 +1746,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1075</v>
+        <v>1093</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1785,10 +1787,12 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>126</v>
-      </c>
-      <c r="G4" t="n">
-        <v>50</v>
+        <v>125</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1826,7 +1830,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -1867,7 +1871,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
         <v>49</v>
@@ -1908,7 +1912,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G7" t="n">
         <v>45</v>
@@ -1949,7 +1953,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11144</v>
+        <v>11231</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1990,7 +1994,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4276</v>
+        <v>4290</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -2031,7 +2035,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -2072,7 +2076,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -2113,7 +2117,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2154,7 +2158,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2496</v>
+        <v>2501</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -2195,7 +2199,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -2236,7 +2240,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -2277,7 +2281,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -2318,7 +2322,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G17" t="n">
         <v>78</v>
@@ -2359,7 +2363,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="G18" t="n">
         <v>49.9</v>
@@ -2400,7 +2404,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11220</v>
+        <v>11240</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -2441,7 +2445,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11064</v>
+        <v>11090</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -2646,7 +2650,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
         <v>49</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
         <v>45</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11231</v>
+        <v>11295</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4290</v>
+        <v>4295</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2501</v>
+        <v>2512</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="G17" t="n">
         <v>78</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="G18" t="n">
         <v>49.9</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11240</v>
+        <v>11257</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11090</v>
+        <v>11114</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
         <v>49</v>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
         <v>45</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11231</v>
+        <v>11295</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4290</v>
+        <v>4295</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2501</v>
+        <v>2512</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="G17" t="n">
         <v>78</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="G18" t="n">
         <v>49.9</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11240</v>
+        <v>11257</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11090</v>
+        <v>11114</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1096</v>
+        <v>1111</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
         <v>49</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
         <v>45</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11295</v>
+        <v>11373</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4295</v>
+        <v>4318</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2512</v>
+        <v>2521</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G17" t="n">
         <v>78</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="G18" t="n">
         <v>49.9</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11257</v>
+        <v>11271</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11114</v>
+        <v>11140</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1514,7 +1514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1559,6 +1559,47 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024.03.03 19:30-03.03 21:00</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1746,7 +1787,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1096</v>
+        <v>1111</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1830,7 +1871,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -1871,7 +1912,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
         <v>49</v>
@@ -1912,7 +1953,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
         <v>45</v>
@@ -1953,7 +1994,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11295</v>
+        <v>11373</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1994,7 +2035,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4295</v>
+        <v>4318</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -2035,7 +2076,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -2076,7 +2117,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -2117,7 +2158,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2158,7 +2199,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2512</v>
+        <v>2521</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -2180,38 +2221,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.03 19:30-03.03 21:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1073</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
         </is>
       </c>
     </row>
@@ -2221,38 +2262,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>112</v>
+        <v>1076</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -2262,38 +2303,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="G16" t="n">
-        <v>29.9</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2303,38 +2344,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>168</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>78</v>
+        <v>29.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -2344,38 +2385,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>492</v>
+        <v>174</v>
       </c>
       <c r="G18" t="n">
-        <v>49.9</v>
+        <v>78</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2385,38 +2426,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11257</v>
+        <v>496</v>
       </c>
       <c r="G19" t="n">
-        <v>59</v>
+        <v>49.9</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2431,33 +2472,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11114</v>
+        <v>11271</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2467,38 +2508,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>11140</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2554,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2527,19 +2568,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2595,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2568,19 +2609,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2636,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2609,19 +2650,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2631,12 +2672,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2646,23 +2687,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2718,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2691,17 +2732,58 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>16</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
         <v>45</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11373</v>
+        <v>11425</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4318</v>
+        <v>4325</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2521</v>
+        <v>2528</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G17" t="n">
         <v>78</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="G18" t="n">
         <v>49.9</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11271</v>
+        <v>11285</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11140</v>
+        <v>11171</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
         <v>45</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11373</v>
+        <v>11425</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4318</v>
+        <v>4325</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2521</v>
+        <v>2528</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G17" t="n">
         <v>29.9</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G18" t="n">
         <v>78</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="G19" t="n">
         <v>49.9</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11271</v>
+        <v>11285</v>
       </c>
       <c r="G20" t="n">
         <v>59</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11140</v>
+        <v>11171</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1117</v>
+        <v>1126</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
         <v>49</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G7" t="n">
         <v>45</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11425</v>
+        <v>11481</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4325</v>
+        <v>4339</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -894,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.24 19:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>45</v>
+        <v>169</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -954,19 +954,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2528</v>
+        <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1076</v>
+        <v>2530</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>123</v>
+        <v>1078</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="G16" t="n">
-        <v>29.9</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
-        <v>78</v>
+        <v>29.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>502</v>
+        <v>1143</v>
       </c>
       <c r="G18" t="n">
-        <v>49.9</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11285</v>
+        <v>177</v>
       </c>
       <c r="G19" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1222,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11171</v>
+        <v>507</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>49.9</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1278,23 +1278,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>11289</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1304,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>11188</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1364,19 +1364,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1405,19 +1405,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1442,23 +1442,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1483,21 +1483,103 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>40</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>16</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1673,7 +1755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1746,7 +1828,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -1787,7 +1869,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1117</v>
+        <v>1126</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1912,7 +1994,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
         <v>49</v>
@@ -1953,7 +2035,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G7" t="n">
         <v>45</v>
@@ -1994,7 +2076,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11425</v>
+        <v>11481</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -2035,7 +2117,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4325</v>
+        <v>4339</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -2117,7 +2199,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -2139,38 +2221,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.24 19:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>45</v>
+        <v>169</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2267,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2199,19 +2281,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2528</v>
+        <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -2221,38 +2303,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.03 19:30-03.03 21:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2530</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -2262,38 +2344,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.03 19:30-03.03 21:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1076</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
         </is>
       </c>
     </row>
@@ -2303,38 +2385,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>123</v>
+        <v>1078</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -2344,38 +2426,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="G17" t="n">
-        <v>29.9</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2385,38 +2467,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="G18" t="n">
-        <v>78</v>
+        <v>29.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -2426,38 +2508,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>502</v>
+        <v>1153</v>
       </c>
       <c r="G19" t="n">
-        <v>49.9</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -2467,38 +2549,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11285</v>
+        <v>177</v>
       </c>
       <c r="G20" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2508,38 +2590,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11171</v>
+        <v>507</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>49.9</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2631,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2564,23 +2646,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>11289</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2590,38 +2672,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>39</v>
+        <v>11188</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2718,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2650,19 +2732,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2759,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2691,19 +2773,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2795,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2728,23 +2810,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2836,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2769,21 +2851,103 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>40</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>16</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11481</v>
+        <v>11511</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4339</v>
+        <v>4345</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
         <v>169</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2530</v>
+        <v>2532</v>
       </c>
       <c r="G14" t="n">
         <v>68</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
         <v>29.9</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1143</v>
+        <v>2214</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11289</v>
+        <v>11298</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11188</v>
+        <v>11207</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11481</v>
+        <v>11511</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4339</v>
+        <v>4345</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
         <v>169</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2530</v>
+        <v>2532</v>
       </c>
       <c r="G14" t="n">
         <v>68</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
         <v>29.9</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1153</v>
+        <v>2214</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="G21" t="n">
         <v>49.9</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11289</v>
+        <v>11298</v>
       </c>
       <c r="G22" t="n">
         <v>59</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11188</v>
+        <v>11207</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1128</v>
+        <v>1336</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11511</v>
+        <v>11564</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4345</v>
+        <v>4361</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
         <v>169</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2532</v>
+        <v>2539</v>
       </c>
       <c r="G14" t="n">
         <v>68</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
         <v>29.9</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2214</v>
+        <v>3634</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11298</v>
+        <v>11316</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11207</v>
+        <v>11231</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1128</v>
+        <v>1336</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11511</v>
+        <v>11564</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4345</v>
+        <v>4361</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
         <v>169</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2532</v>
+        <v>2539</v>
       </c>
       <c r="G14" t="n">
         <v>68</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" t="n">
         <v>29.9</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2214</v>
+        <v>3634</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11298</v>
+        <v>11316</v>
       </c>
       <c r="G22" t="n">
         <v>59</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11207</v>
+        <v>11231</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11564</v>
+        <v>11592</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4361</v>
+        <v>4367</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="G14" t="n">
         <v>68</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G17" t="n">
         <v>29.9</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3634</v>
+        <v>4670</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11316</v>
+        <v>11323</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11231</v>
+        <v>11245</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11564</v>
+        <v>11592</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4361</v>
+        <v>4367</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="G14" t="n">
         <v>68</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G18" t="n">
         <v>29.9</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3634</v>
+        <v>4670</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11316</v>
+        <v>11323</v>
       </c>
       <c r="G22" t="n">
         <v>59</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11231</v>
+        <v>11245</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1340</v>
+        <v>1347</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -648,38 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -694,33 +694,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>62</v>
+        <v>11634</v>
       </c>
       <c r="G7" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11592</v>
+        <v>4373</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4367</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -817,33 +817,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -858,33 +858,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 13:00-02.24 19:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.24 19:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -954,19 +954,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>2543</v>
       </c>
       <c r="G13" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2541</v>
+        <v>1091</v>
       </c>
       <c r="G14" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1090</v>
+        <v>141</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>29.9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>5066</v>
       </c>
       <c r="G17" t="n">
-        <v>29.9</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4670</v>
+        <v>61</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11323</v>
+        <v>11327</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11245</v>
+        <v>11254</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1340</v>
+        <v>1347</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -1975,38 +1975,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -2021,33 +2021,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>62</v>
+        <v>11634</v>
       </c>
       <c r="G7" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2076,19 +2076,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11592</v>
+        <v>4373</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -2098,38 +2098,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4367</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -2144,33 +2144,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -2185,33 +2185,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 13:00-02.24 19:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
         </is>
       </c>
     </row>
@@ -2221,38 +2221,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.24 19:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2281,19 +2281,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>2543</v>
       </c>
       <c r="G13" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -2303,38 +2303,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.03 19:30-03.03 21:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2541</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
         </is>
       </c>
     </row>
@@ -2344,38 +2344,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.03 19:30-03.03 21:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>1091</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -2385,38 +2385,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1090</v>
+        <v>141</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2426,38 +2426,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>29.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -2467,38 +2467,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>5066</v>
       </c>
       <c r="G18" t="n">
-        <v>29.9</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -2508,38 +2508,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4670</v>
+        <v>61</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G21" t="n">
         <v>49.9</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11323</v>
+        <v>11327</v>
       </c>
       <c r="G22" t="n">
         <v>59</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11245</v>
+        <v>11254</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11634</v>
+        <v>11659</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4373</v>
+        <v>4381</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
         <v>169</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2543</v>
+        <v>2545</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5066</v>
+        <v>5080</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G18" t="n">
         <v>49</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11327</v>
+        <v>11329</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11254</v>
+        <v>11261</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11634</v>
+        <v>11659</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4373</v>
+        <v>4381</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
         <v>169</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2543</v>
+        <v>2545</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
         <v>29.9</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5066</v>
+        <v>5080</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G19" t="n">
         <v>49</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G21" t="n">
         <v>49.9</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11327</v>
+        <v>11329</v>
       </c>
       <c r="G22" t="n">
         <v>59</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11254</v>
+        <v>11261</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1351</v>
+        <v>1364</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11659</v>
+        <v>11700</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4381</v>
+        <v>4391</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2545</v>
+        <v>2548</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5080</v>
+        <v>5105</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G18" t="n">
         <v>49</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11329</v>
+        <v>11346</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11261</v>
+        <v>11275</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1351</v>
+        <v>1364</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11659</v>
+        <v>11700</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4381</v>
+        <v>4391</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2545</v>
+        <v>2548</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
         <v>29.9</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5080</v>
+        <v>5105</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G19" t="n">
         <v>49</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G21" t="n">
         <v>49.9</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11329</v>
+        <v>11346</v>
       </c>
       <c r="G22" t="n">
         <v>59</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11261</v>
+        <v>11275</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1364</v>
+        <v>1373</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11700</v>
+        <v>11737</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4391</v>
+        <v>4400</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
         <v>169</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2548</v>
+        <v>2551</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5105</v>
+        <v>5116</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11346</v>
+        <v>11353</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11275</v>
+        <v>11293</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1364</v>
+        <v>1373</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11700</v>
+        <v>11737</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4391</v>
+        <v>4400</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
         <v>169</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2548</v>
+        <v>2551</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G17" t="n">
         <v>29.9</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5105</v>
+        <v>5116</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="G21" t="n">
         <v>49.9</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11346</v>
+        <v>11353</v>
       </c>
       <c r="G22" t="n">
         <v>59</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11275</v>
+        <v>11293</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1373</v>
+        <v>1387</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11737</v>
+        <v>11790</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4400</v>
+        <v>4413</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
         <v>169</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2551</v>
+        <v>2556</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5116</v>
+        <v>5127</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11353</v>
+        <v>11364</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11293</v>
+        <v>11313</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1373</v>
+        <v>1387</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11737</v>
+        <v>11790</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4400</v>
+        <v>4413</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
         <v>169</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2551</v>
+        <v>2556</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G17" t="n">
         <v>29.9</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5116</v>
+        <v>5127</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="G21" t="n">
         <v>49.9</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11353</v>
+        <v>11364</v>
       </c>
       <c r="G22" t="n">
         <v>59</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11293</v>
+        <v>11313</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11790</v>
+        <v>11824</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4413</v>
+        <v>4419</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5127</v>
+        <v>5132</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11364</v>
+        <v>11373</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11313</v>
+        <v>11335</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11790</v>
+        <v>11824</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4413</v>
+        <v>4419</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
         <v>29.9</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5127</v>
+        <v>5132</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="G21" t="n">
         <v>49.9</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11364</v>
+        <v>11373</v>
       </c>
       <c r="G22" t="n">
         <v>59</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11313</v>
+        <v>11335</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1393</v>
+        <v>1402</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11824</v>
+        <v>11878</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4419</v>
+        <v>4436</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2557</v>
+        <v>2565</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5132</v>
+        <v>5152</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11373</v>
+        <v>11383</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11335</v>
+        <v>11364</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1393</v>
+        <v>1402</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11824</v>
+        <v>11878</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4419</v>
+        <v>4436</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2557</v>
+        <v>2565</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G17" t="n">
         <v>29.9</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5132</v>
+        <v>5152</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G21" t="n">
         <v>49.9</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11373</v>
+        <v>11383</v>
       </c>
       <c r="G22" t="n">
         <v>59</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11335</v>
+        <v>11364</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1402</v>
+        <v>1409</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11878</v>
+        <v>11901</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4436</v>
+        <v>4442</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2565</v>
+        <v>2568</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5152</v>
+        <v>5163</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11383</v>
+        <v>11388</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11364</v>
+        <v>11376</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1402</v>
+        <v>1409</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11878</v>
+        <v>11901</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4436</v>
+        <v>4442</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2565</v>
+        <v>2568</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5152</v>
+        <v>5163</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="G21" t="n">
         <v>49.9</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11383</v>
+        <v>11388</v>
       </c>
       <c r="G22" t="n">
         <v>59</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11364</v>
+        <v>11376</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1409</v>
+        <v>1430</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11901</v>
+        <v>11964</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4442</v>
+        <v>4447</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G11" t="n">
         <v>169</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2568</v>
+        <v>2571</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5163</v>
+        <v>5178</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11388</v>
+        <v>11395</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11376</v>
+        <v>11406</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1409</v>
+        <v>1430</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11901</v>
+        <v>11964</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4442</v>
+        <v>4447</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G11" t="n">
         <v>169</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
         <v>45</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2568</v>
+        <v>2571</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G17" t="n">
         <v>29.9</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5163</v>
+        <v>5178</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="G21" t="n">
         <v>49.9</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11388</v>
+        <v>11395</v>
       </c>
       <c r="G22" t="n">
         <v>59</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11376</v>
+        <v>11406</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11964</v>
+        <v>11994</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4447</v>
+        <v>4456</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
         <v>169</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2571</v>
+        <v>2576</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G16" t="n">
         <v>29.9</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5178</v>
+        <v>5195</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G20" t="n">
         <v>49.9</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11395</v>
+        <v>11402</v>
       </c>
       <c r="G21" t="n">
         <v>59</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11406</v>
+        <v>11424</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11964</v>
+        <v>11994</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4447</v>
+        <v>4456</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
         <v>169</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2571</v>
+        <v>2576</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G17" t="n">
         <v>29.9</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5178</v>
+        <v>5195</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G21" t="n">
         <v>49.9</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11395</v>
+        <v>11402</v>
       </c>
       <c r="G22" t="n">
         <v>59</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11406</v>
+        <v>11424</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024.02.08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -523,7 +523,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1434</v>
+        <v>1447</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -564,7 +564,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -607,38 +607,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>张家港·META萌元漫展</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -648,38 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>12059</v>
       </c>
       <c r="G6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -689,12 +689,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -708,19 +708,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11994</v>
+        <v>4463</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -730,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4456</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -812,38 +812,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 13:00-02.24 19:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,38 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.24 19:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G11" t="n">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,17 +894,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -913,19 +913,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>2585</v>
       </c>
       <c r="G12" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2576</v>
+        <v>1117</v>
       </c>
       <c r="G13" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1114</v>
+        <v>179</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>175</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>29.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>57</v>
+        <v>5216</v>
       </c>
       <c r="G16" t="n">
-        <v>29.9</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5195</v>
+        <v>63</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>63</v>
+        <v>199</v>
       </c>
       <c r="G18" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>197</v>
+        <v>542</v>
       </c>
       <c r="G19" t="n">
-        <v>78</v>
+        <v>49.9</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1222,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>540</v>
+        <v>11409</v>
       </c>
       <c r="G20" t="n">
-        <v>49.9</v>
+        <v>59</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11402</v>
+        <v>11455</v>
       </c>
       <c r="G21" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1304,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11424</v>
+        <v>22</v>
       </c>
       <c r="G22" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1364,19 +1364,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1405,19 +1405,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1446,19 +1446,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1483,23 +1483,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1528,58 +1528,17 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>26</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1650,7 +1609,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1755,7 +1714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1809,7 +1768,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024.02.08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1828,7 +1787,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -1850,7 +1809,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1869,7 +1828,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1434</v>
+        <v>1447</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1891,7 +1850,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1934,38 +1893,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>张家港·META萌元漫展</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>杨舍镇福新路附近 喜福遇婚庆店</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81189</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yhLkC15b1705912912966.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -1975,38 +1934,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>12059</v>
       </c>
       <c r="G6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -2016,12 +1975,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2035,19 +1994,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11994</v>
+        <v>4463</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -2057,38 +2016,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4456</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -2098,38 +2057,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -2139,38 +2098,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 13:00-02.24 19:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
         </is>
       </c>
     </row>
@@ -2180,38 +2139,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.24 19:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G11" t="n">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -2221,17 +2180,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2240,19 +2199,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>2585</v>
       </c>
       <c r="G12" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -2262,38 +2221,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.03 19:30-03.03 21:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2576</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
         </is>
       </c>
     </row>
@@ -2303,38 +2262,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.03 19:30-03.03 21:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>1117</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -2344,38 +2303,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1114</v>
+        <v>179</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2385,38 +2344,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>175</v>
+        <v>58</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>29.9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -2426,38 +2385,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>5216</v>
       </c>
       <c r="G17" t="n">
-        <v>29.9</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -2467,38 +2426,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5195</v>
+        <v>63</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -2508,38 +2467,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>63</v>
+        <v>199</v>
       </c>
       <c r="G19" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2549,38 +2508,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>197</v>
+        <v>542</v>
       </c>
       <c r="G20" t="n">
-        <v>78</v>
+        <v>49.9</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2590,38 +2549,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>540</v>
+        <v>11409</v>
       </c>
       <c r="G21" t="n">
-        <v>49.9</v>
+        <v>59</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2631,38 +2590,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11402</v>
+        <v>11455</v>
       </c>
       <c r="G22" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2672,38 +2631,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11424</v>
+        <v>22</v>
       </c>
       <c r="G23" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2672,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2732,19 +2691,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2713,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2773,19 +2732,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2795,12 +2754,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2814,19 +2773,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2836,12 +2795,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2851,23 +2810,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -2877,12 +2836,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2896,58 +2855,17 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>26</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -564,40 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.14</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>常熟·漫魂动漫游戏展01</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>虞山北路258号 星程酒店</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 21:00</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>128</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>74</v>
+      </c>
+      <c r="G4" t="n">
+        <v>45</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -612,33 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>12100</v>
       </c>
       <c r="G5" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -653,7 +651,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -667,19 +665,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>12059</v>
+        <v>4471</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -689,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4463</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -735,33 +733,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -776,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 13:00-02.24 19:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
         </is>
       </c>
     </row>
@@ -812,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.24 19:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -858,12 +856,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -872,19 +870,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>2587</v>
       </c>
       <c r="G11" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2585</v>
+        <v>1118</v>
       </c>
       <c r="G12" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,38 +933,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1117</v>
+        <v>181</v>
       </c>
       <c r="G13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +974,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>29.9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1015,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>58</v>
+        <v>5239</v>
       </c>
       <c r="G15" t="n">
-        <v>29.9</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1056,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5216</v>
+        <v>63</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1097,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>63</v>
+        <v>204</v>
       </c>
       <c r="G17" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1138,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>199</v>
+        <v>544</v>
       </c>
       <c r="G18" t="n">
-        <v>78</v>
+        <v>49.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1179,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>542</v>
+        <v>11420</v>
       </c>
       <c r="G19" t="n">
-        <v>49.9</v>
+        <v>59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1227,33 +1225,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11409</v>
+        <v>11479</v>
       </c>
       <c r="G20" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1261,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11455</v>
+        <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1307,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1323,19 +1321,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1348,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1364,19 +1362,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1389,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1405,19 +1403,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1425,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1442,23 +1440,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1471,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1487,58 +1485,17 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>26</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1714,7 +1671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1828,7 +1785,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -1850,40 +1807,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.14</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>常熟·漫魂动漫游戏展01</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>虞山北路258号 星程酒店</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.14 21:00</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>128</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>74</v>
+      </c>
+      <c r="G4" t="n">
+        <v>45</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80248</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/oPrKUOby1703664065719.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -1898,33 +1853,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>12100</v>
       </c>
       <c r="G5" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1894,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1953,19 +1908,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>12059</v>
+        <v>4471</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -1975,38 +1930,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4463</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -2021,33 +1976,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -2062,33 +2017,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 13:00-02.24 19:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
         </is>
       </c>
     </row>
@@ -2098,38 +2053,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.24 19:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2099,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2158,19 +2113,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>2587</v>
       </c>
       <c r="G11" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -2180,38 +2135,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.03 19:30-03.03 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2585</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
         </is>
       </c>
     </row>
@@ -2221,38 +2176,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.03 19:30-03.03 21:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>1118</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -2262,38 +2217,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1117</v>
+        <v>181</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2303,38 +2258,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>29.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -2344,38 +2299,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>58</v>
+        <v>5239</v>
       </c>
       <c r="G16" t="n">
-        <v>29.9</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -2385,38 +2340,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5216</v>
+        <v>63</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -2426,38 +2381,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>63</v>
+        <v>204</v>
       </c>
       <c r="G18" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2467,38 +2422,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>199</v>
+        <v>544</v>
       </c>
       <c r="G19" t="n">
-        <v>78</v>
+        <v>49.9</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2508,38 +2463,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>542</v>
+        <v>11420</v>
       </c>
       <c r="G20" t="n">
-        <v>49.9</v>
+        <v>59</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2554,33 +2509,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11409</v>
+        <v>11479</v>
       </c>
       <c r="G21" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2590,38 +2545,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11455</v>
+        <v>22</v>
       </c>
       <c r="G22" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2591,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2650,19 +2605,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2632,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2691,19 +2646,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2673,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2732,19 +2687,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2709,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2769,23 +2724,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2755,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2814,58 +2769,17 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>26</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.14</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>常熟·CDW·动漫展02</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>常熟国际展览中心 国际展览中心</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:30</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1450</v>
+        <v>73</v>
       </c>
       <c r="G3" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -569,33 +569,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>12163</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -624,19 +624,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12100</v>
+        <v>4481</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4471</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -692,33 +692,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -733,33 +733,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 13:00-02.24 19:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.24 19:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>2595</v>
       </c>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -851,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2587</v>
+        <v>1125</v>
       </c>
       <c r="G11" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -892,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1118</v>
+        <v>190</v>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -933,38 +933,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>29.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -974,38 +974,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>61</v>
+        <v>5268</v>
       </c>
       <c r="G14" t="n">
-        <v>29.9</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -1015,38 +1015,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5239</v>
+        <v>65</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1056,38 +1056,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>63</v>
+        <v>205</v>
       </c>
       <c r="G16" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1097,38 +1097,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>204</v>
+        <v>548</v>
       </c>
       <c r="G17" t="n">
-        <v>78</v>
+        <v>49.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1138,38 +1138,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>544</v>
+        <v>11443</v>
       </c>
       <c r="G18" t="n">
-        <v>49.9</v>
+        <v>59</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1184,33 +1184,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11420</v>
+        <v>11510</v>
       </c>
       <c r="G19" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1220,38 +1220,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11479</v>
+        <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1280,19 +1280,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1399,23 +1399,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1444,58 +1444,17 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>26</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1671,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1766,38 +1725,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.14</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>常熟·CDW·动漫展02</t>
+          <t>太仓·龙狮新春动漫节4.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>常熟国际展览中心 国际展览中心</t>
+          <t>滨河路126号 凯景世纪大酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.14 09:00-02.15 17:30</t>
+          <t>2024.02.16 08:30-02.16 15:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1450</v>
+        <v>73</v>
       </c>
       <c r="G3" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/VHHzVjad1704438989848.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
         </is>
       </c>
     </row>
@@ -1812,33 +1771,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>12163</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1812,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1867,19 +1826,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12100</v>
+        <v>4481</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -1889,38 +1848,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4471</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -1935,33 +1894,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -1976,33 +1935,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 13:00-02.24 19:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
         </is>
       </c>
     </row>
@@ -2012,38 +1971,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.24 19:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -2058,12 +2017,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2072,19 +2031,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>2595</v>
       </c>
       <c r="G10" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -2094,38 +2053,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.03 19:30-03.03 21:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2587</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
         </is>
       </c>
     </row>
@@ -2135,38 +2094,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.03 19:30-03.03 21:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>1125</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -2176,38 +2135,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1118</v>
+        <v>190</v>
       </c>
       <c r="G13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2217,38 +2176,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>29.9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -2258,38 +2217,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>61</v>
+        <v>5268</v>
       </c>
       <c r="G15" t="n">
-        <v>29.9</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -2299,38 +2258,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5239</v>
+        <v>65</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -2340,38 +2299,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>63</v>
+        <v>205</v>
       </c>
       <c r="G17" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2381,38 +2340,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>204</v>
+        <v>548</v>
       </c>
       <c r="G18" t="n">
-        <v>78</v>
+        <v>49.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2422,38 +2381,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>544</v>
+        <v>11443</v>
       </c>
       <c r="G19" t="n">
-        <v>49.9</v>
+        <v>59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2468,33 +2427,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11420</v>
+        <v>11510</v>
       </c>
       <c r="G20" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2504,38 +2463,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11479</v>
+        <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2509,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2564,19 +2523,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2550,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2605,19 +2564,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2591,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2646,19 +2605,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2627,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2683,23 +2642,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2673,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2728,58 +2687,17 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>26</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>12163</v>
+        <v>12198</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4481</v>
+        <v>4486</v>
       </c>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
         <v>20</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2595</v>
+        <v>2604</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="G11" t="n">
         <v>65</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G13" t="n">
         <v>29.9</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5268</v>
+        <v>5296</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15" t="n">
         <v>49</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G16" t="n">
         <v>78</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="G17" t="n">
         <v>49.9</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11443</v>
+        <v>11460</v>
       </c>
       <c r="G18" t="n">
         <v>59</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11510</v>
+        <v>11534</v>
       </c>
       <c r="G19" t="n">
         <v>65</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>12163</v>
+        <v>12198</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4481</v>
+        <v>4486</v>
       </c>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
         <v>20</v>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2595</v>
+        <v>2604</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
         <v>29.9</v>
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5268</v>
+        <v>5296</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G16" t="n">
         <v>49</v>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G17" t="n">
         <v>78</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="G18" t="n">
         <v>49.9</v>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11443</v>
+        <v>11460</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11510</v>
+        <v>11534</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,33 +528,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>12236</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,19 +583,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>12198</v>
+        <v>4497</v>
       </c>
       <c r="G4" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4486</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -651,33 +651,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -692,33 +692,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 13:00-02.24 19:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
         </is>
       </c>
     </row>
@@ -728,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.24 19:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -788,19 +788,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>2612</v>
       </c>
       <c r="G9" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -810,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2604</v>
+        <v>1133</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -851,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1129</v>
+        <v>206</v>
       </c>
       <c r="G11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -892,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>29.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -933,38 +933,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>5327</v>
       </c>
       <c r="G13" t="n">
-        <v>29.9</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -974,38 +974,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5296</v>
+        <v>66</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1015,38 +1015,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>66</v>
+        <v>213</v>
       </c>
       <c r="G15" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1056,38 +1056,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>206</v>
+        <v>560</v>
       </c>
       <c r="G16" t="n">
-        <v>78</v>
+        <v>49.9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1097,38 +1097,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>555</v>
+        <v>11487</v>
       </c>
       <c r="G17" t="n">
-        <v>49.9</v>
+        <v>59</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1143,33 +1143,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11460</v>
+        <v>11585</v>
       </c>
       <c r="G18" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1179,38 +1179,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11534</v>
+        <v>22</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1239,19 +1239,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1280,19 +1280,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1358,23 +1358,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1403,58 +1403,17 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>27</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1630,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1730,33 +1689,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>太仓·龙狮新春动漫节4.0</t>
+          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>滨河路126号 凯景世纪大酒店</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.16 08:30-02.16 15:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>12236</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81044</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/AMDXVltp1705568031796.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1730,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>苏州·运动番only专区-Good jump ACG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1785,19 +1744,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>12198</v>
+        <v>4497</v>
       </c>
       <c r="G4" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
         </is>
       </c>
     </row>
@@ -1807,38 +1766,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4486</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -1853,33 +1812,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -1894,33 +1853,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 13:00-02.24 19:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
         </is>
       </c>
     </row>
@@ -1930,38 +1889,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.24 19:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>169</v>
+        <v>45</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1990,19 +1949,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>2612</v>
       </c>
       <c r="G9" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -2012,38 +1971,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.03 19:30-03.03 21:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2604</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
         </is>
       </c>
     </row>
@@ -2053,38 +2012,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.03 19:30-03.03 21:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>1133</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -2094,38 +2053,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1129</v>
+        <v>206</v>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2135,38 +2094,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>29.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -2176,38 +2135,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>70</v>
+        <v>5327</v>
       </c>
       <c r="G14" t="n">
-        <v>29.9</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -2217,38 +2176,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5296</v>
+        <v>66</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -2258,38 +2217,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>66</v>
+        <v>213</v>
       </c>
       <c r="G16" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2299,38 +2258,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>206</v>
+        <v>560</v>
       </c>
       <c r="G17" t="n">
-        <v>78</v>
+        <v>49.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2340,38 +2299,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>555</v>
+        <v>11487</v>
       </c>
       <c r="G18" t="n">
-        <v>49.9</v>
+        <v>59</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2386,33 +2345,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11460</v>
+        <v>11585</v>
       </c>
       <c r="G19" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2422,38 +2381,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11534</v>
+        <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2427,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2482,19 +2441,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2468,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2523,19 +2482,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2509,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2564,19 +2523,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2545,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2601,23 +2560,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2591,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2646,58 +2605,17 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>27</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12236</v>
+        <v>12251</v>
       </c>
       <c r="G3" t="n">
         <v>70</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4497</v>
+        <v>4498</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
         <v>20</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
         <v>169</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2612</v>
+        <v>2616</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G12" t="n">
         <v>29.9</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5327</v>
+        <v>5355</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14" t="n">
         <v>49</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G15" t="n">
         <v>78</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="G16" t="n">
         <v>49.9</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11487</v>
+        <v>11505</v>
       </c>
       <c r="G17" t="n">
         <v>59</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11585</v>
+        <v>11617</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12236</v>
+        <v>12251</v>
       </c>
       <c r="G3" t="n">
         <v>70</v>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4497</v>
+        <v>4498</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
         <v>20</v>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
         <v>169</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
         <v>45</v>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2612</v>
+        <v>2616</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="G11" t="n">
         <v>65</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
         <v>29.9</v>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5327</v>
+        <v>5355</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15" t="n">
         <v>49</v>
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G16" t="n">
         <v>78</v>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="G17" t="n">
         <v>49.9</v>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11487</v>
+        <v>11505</v>
       </c>
       <c r="G18" t="n">
         <v>59</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11585</v>
+        <v>11617</v>
       </c>
       <c r="G19" t="n">
         <v>65</v>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12251</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4498</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -610,33 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 13:00-02.24 19:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>169</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.24 19:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>2625</v>
       </c>
       <c r="G7" t="n">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -728,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="G8" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,12 +769,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -784,23 +784,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2616</v>
+        <v>224</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -810,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1137</v>
+        <v>88</v>
       </c>
       <c r="G10" t="n">
-        <v>65</v>
+        <v>29.9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -851,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>213</v>
+        <v>5785</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -892,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="G12" t="n">
-        <v>29.9</v>
+        <v>49</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -933,38 +933,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5355</v>
+        <v>228</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -974,38 +974,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>67</v>
+        <v>574</v>
       </c>
       <c r="G14" t="n">
-        <v>49</v>
+        <v>49.9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1015,38 +1015,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>218</v>
+        <v>11545</v>
       </c>
       <c r="G15" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1056,38 +1056,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>566</v>
+        <v>11701</v>
       </c>
       <c r="G16" t="n">
-        <v>49.9</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1112,23 +1112,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11505</v>
+        <v>23</v>
       </c>
       <c r="G17" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1138,38 +1138,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11617</v>
+        <v>71</v>
       </c>
       <c r="G18" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1239,19 +1239,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1276,23 +1276,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1317,103 +1317,21 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>58</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>26</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1589,7 +1507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1662,7 +1580,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -1684,38 +1602,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>苏州·Good Jump ACG迎新特别篇X动漫品牌博览会</t>
+          <t>张家港·上元节AF 汉服花灯动漫展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 09:30-02.24 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12251</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79303</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/C3P0Encm1701659824998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
         </is>
       </c>
     </row>
@@ -1725,38 +1643,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·运动番only专区-Good jump ACG</t>
+          <t>苏州·世纪幻想动漫游戏展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>相城大道1609号 苏州环球港</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4498</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81435</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/gatL3YjP1706236832019.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
         </is>
       </c>
     </row>
@@ -1771,33 +1689,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.24 13:00-02.24 19:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>169</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
         </is>
       </c>
     </row>
@@ -1807,38 +1725,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1848,38 +1766,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
+          <t>苏州·第五届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.24 19:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>2625</v>
       </c>
       <c r="G7" t="n">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -1889,38 +1807,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.03 19:30-03.03 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
         </is>
       </c>
     </row>
@@ -1930,38 +1848,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·国风宠物-cosplay展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2616</v>
+        <v>1140</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -1971,38 +1889,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.03 19:30-03.03 21:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>224</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2012,38 +1930,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1137</v>
+        <v>88</v>
       </c>
       <c r="G11" t="n">
-        <v>65</v>
+        <v>29.9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -2053,38 +1971,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>213</v>
+        <v>5785</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -2094,38 +2012,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="G13" t="n">
-        <v>29.9</v>
+        <v>49</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -2135,38 +2053,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5355</v>
+        <v>228</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2176,38 +2094,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>67</v>
+        <v>574</v>
       </c>
       <c r="G15" t="n">
-        <v>49</v>
+        <v>49.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2217,38 +2135,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>218</v>
+        <v>11545</v>
       </c>
       <c r="G16" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2258,38 +2176,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>566</v>
+        <v>11701</v>
       </c>
       <c r="G17" t="n">
-        <v>49.9</v>
+        <v>65</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2299,12 +2217,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2314,23 +2232,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11505</v>
+        <v>23</v>
       </c>
       <c r="G18" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2340,38 +2258,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11617</v>
+        <v>71</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2304,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2400,19 +2318,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2345,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2441,19 +2359,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2463,12 +2381,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2478,23 +2396,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2422,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2519,103 +2437,21 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>58</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>26</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2625</v>
+        <v>2630</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1140</v>
+        <v>1145</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G10" t="n">
         <v>29.9</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5785</v>
+        <v>5906</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G13" t="n">
         <v>78</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="G14" t="n">
         <v>49.9</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>11545</v>
+        <v>11581</v>
       </c>
       <c r="G15" t="n">
         <v>59</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11701</v>
+        <v>11774</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2625</v>
+        <v>2630</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1140</v>
+        <v>1145</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G11" t="n">
         <v>29.9</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5785</v>
+        <v>5906</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" t="n">
         <v>49</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G14" t="n">
         <v>78</v>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="G15" t="n">
         <v>49.9</v>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11545</v>
+        <v>11581</v>
       </c>
       <c r="G16" t="n">
         <v>59</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11701</v>
+        <v>11774</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
         <v>169</v>
@@ -636,7 +636,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/BqSjvdLT1708224342995.png</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2630</v>
+        <v>2645</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1145</v>
+        <v>1156</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G10" t="n">
         <v>29.9</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5906</v>
+        <v>7696</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G13" t="n">
         <v>78</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="G14" t="n">
         <v>49.9</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>11581</v>
+        <v>11627</v>
       </c>
       <c r="G15" t="n">
         <v>59</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11774</v>
+        <v>11884</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
         <v>169</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QcC9Z3MQ1707275914021.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/BqSjvdLT1708224342995.png</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2630</v>
+        <v>2645</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1145</v>
+        <v>1156</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G11" t="n">
         <v>29.9</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5906</v>
+        <v>7706</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G14" t="n">
         <v>78</v>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="G15" t="n">
         <v>49.9</v>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11581</v>
+        <v>11627</v>
       </c>
       <c r="G16" t="n">
         <v>59</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11774</v>
+        <v>11884</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
         <v>169</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2645</v>
+        <v>2654</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G10" t="n">
         <v>29.9</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>7696</v>
+        <v>9747</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G13" t="n">
         <v>78</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="G14" t="n">
         <v>49.9</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>11627</v>
+        <v>11666</v>
       </c>
       <c r="G15" t="n">
         <v>59</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11884</v>
+        <v>11953</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
         <v>169</v>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2645</v>
+        <v>2654</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G11" t="n">
         <v>29.9</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>7706</v>
+        <v>9747</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G14" t="n">
         <v>78</v>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="G15" t="n">
         <v>49.9</v>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11627</v>
+        <v>11666</v>
       </c>
       <c r="G16" t="n">
         <v>59</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11884</v>
+        <v>11953</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -677,7 +677,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IwXBoz7t1708330463199.jpeg</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2654</v>
+        <v>2663</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G10" t="n">
         <v>29.9</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>9747</v>
+        <v>9818</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="G13" t="n">
         <v>78</v>
@@ -974,38 +974,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>591</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>49.9</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -1015,38 +1015,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>11666</v>
+        <v>603</v>
       </c>
       <c r="G15" t="n">
-        <v>59</v>
+        <v>49.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1061,33 +1061,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11953</v>
+        <v>11702</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1097,38 +1097,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
+        <v>12021</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1157,19 +1157,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1239,19 +1239,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.05.03</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1276,23 +1276,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1321,17 +1321,58 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2024.05.03</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>32</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1507,7 +1548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1621,7 +1662,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -1744,7 +1785,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -1756,7 +1797,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/lVVrbSra1706508320671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IwXBoz7t1708330463199.jpeg</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1826,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2654</v>
+        <v>2663</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -1867,7 +1908,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -1908,7 +1949,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -1949,7 +1990,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G11" t="n">
         <v>29.9</v>
@@ -1990,7 +2031,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9747</v>
+        <v>9818</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -2031,7 +2072,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" t="n">
         <v>49</v>
@@ -2072,7 +2113,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="G14" t="n">
         <v>78</v>
@@ -2094,38 +2135,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>591</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>49.9</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -2135,38 +2176,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11666</v>
+        <v>603</v>
       </c>
       <c r="G16" t="n">
-        <v>59</v>
+        <v>49.9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2181,33 +2222,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11953</v>
+        <v>11702</v>
       </c>
       <c r="G17" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2217,38 +2258,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>24</v>
+        <v>12021</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2304,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2277,19 +2318,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2345,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2318,19 +2359,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2386,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2359,19 +2400,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2422,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.05.03</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2396,23 +2437,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2468,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2441,17 +2482,58 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2024.05.03</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>32</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
         <v>169</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2663</v>
+        <v>2668</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G10" t="n">
         <v>29.9</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>9818</v>
+        <v>9921</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G13" t="n">
         <v>78</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>603</v>
+        <v>612</v>
       </c>
       <c r="G15" t="n">
         <v>49.9</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11702</v>
+        <v>11732</v>
       </c>
       <c r="G16" t="n">
         <v>59</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>12021</v>
+        <v>12065</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
         <v>169</v>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2663</v>
+        <v>2668</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G11" t="n">
         <v>29.9</v>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9818</v>
+        <v>9924</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G14" t="n">
         <v>78</v>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>603</v>
+        <v>612</v>
       </c>
       <c r="G16" t="n">
         <v>49.9</v>
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11702</v>
+        <v>11732</v>
       </c>
       <c r="G17" t="n">
         <v>59</v>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>12021</v>
+        <v>12065</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2668</v>
+        <v>2677</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -733,7 +733,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·国风宠物-cosplay展（取消）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -747,10 +747,12 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1167</v>
-      </c>
-      <c r="G8" t="n">
-        <v>65</v>
+        <v>1168</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -800,7 +802,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/BkAdM9dY1708409139899.jpeg</t>
         </is>
       </c>
     </row>
@@ -829,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G10" t="n">
         <v>29.9</v>
@@ -870,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>9921</v>
+        <v>10065</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -911,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -952,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G13" t="n">
         <v>78</v>
@@ -993,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="G15" t="n">
         <v>49.9</v>
@@ -1075,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11732</v>
+        <v>11757</v>
       </c>
       <c r="G16" t="n">
         <v>59</v>
@@ -1116,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>12065</v>
+        <v>12113</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -1157,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1198,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -1280,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -1362,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1462,7 +1464,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1662,7 +1664,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -1703,7 +1705,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -1785,7 +1787,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -1826,7 +1828,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2668</v>
+        <v>2677</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -1867,7 +1869,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1894,7 +1896,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展</t>
+          <t>苏州·国风宠物-cosplay展（取消）</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1908,10 +1910,12 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1167</v>
-      </c>
-      <c r="G9" t="n">
-        <v>65</v>
+        <v>1168</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1949,7 +1953,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -1961,7 +1965,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/m0Q2ZB3L1706153205872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/BkAdM9dY1708409139899.jpeg</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1994,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G11" t="n">
         <v>29.9</v>
@@ -2031,7 +2035,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9924</v>
+        <v>10065</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -2072,7 +2076,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G13" t="n">
         <v>49</v>
@@ -2113,7 +2117,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G14" t="n">
         <v>78</v>
@@ -2154,7 +2158,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -2195,7 +2199,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="G16" t="n">
         <v>49.9</v>
@@ -2236,7 +2240,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11732</v>
+        <v>11757</v>
       </c>
       <c r="G17" t="n">
         <v>59</v>
@@ -2277,7 +2281,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>12065</v>
+        <v>12113</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -2318,7 +2322,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -2359,7 +2363,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -2441,7 +2445,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -2523,7 +2527,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2677</v>
+        <v>2685</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G10" t="n">
         <v>29.9</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10065</v>
+        <v>10105</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G13" t="n">
         <v>78</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="G15" t="n">
         <v>49.9</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11757</v>
+        <v>11772</v>
       </c>
       <c r="G16" t="n">
         <v>59</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>12113</v>
+        <v>12143</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2677</v>
+        <v>2685</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G11" t="n">
         <v>29.9</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10065</v>
+        <v>10105</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G13" t="n">
         <v>49</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G14" t="n">
         <v>78</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="G16" t="n">
         <v>49.9</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11757</v>
+        <v>11772</v>
       </c>
       <c r="G17" t="n">
         <v>59</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>12113</v>
+        <v>12143</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2685</v>
+        <v>2693</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="G10" t="n">
         <v>29.9</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10105</v>
+        <v>10162</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G13" t="n">
         <v>78</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="G15" t="n">
         <v>49.9</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11772</v>
+        <v>11796</v>
       </c>
       <c r="G16" t="n">
         <v>59</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>12143</v>
+        <v>12187</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
         <v>39.9</v>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2685</v>
+        <v>2693</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="G11" t="n">
         <v>29.9</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10105</v>
+        <v>10162</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G13" t="n">
         <v>49</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G14" t="n">
         <v>78</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="G16" t="n">
         <v>49.9</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11772</v>
+        <v>11796</v>
       </c>
       <c r="G17" t="n">
         <v>59</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>12143</v>
+        <v>12187</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
         <v>169</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2693</v>
+        <v>2703</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G10" t="n">
         <v>29.9</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10162</v>
+        <v>10197</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G13" t="n">
         <v>78</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G15" t="n">
         <v>49.9</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11796</v>
+        <v>11808</v>
       </c>
       <c r="G16" t="n">
         <v>59</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>12187</v>
+        <v>12214</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
         <v>169</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2693</v>
+        <v>2703</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G11" t="n">
         <v>29.9</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10162</v>
+        <v>10197</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G14" t="n">
         <v>78</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G16" t="n">
         <v>49.9</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11796</v>
+        <v>11808</v>
       </c>
       <c r="G17" t="n">
         <v>59</v>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>12187</v>
+        <v>12214</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>169</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -692,7 +692,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展（取消）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -706,10 +706,12 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2703</v>
-      </c>
-      <c r="G7" t="n">
-        <v>68</v>
+        <v>2707</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -790,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>282</v>
+        <v>410</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -802,7 +804,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/BkAdM9dY1708409139899.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
         </is>
       </c>
     </row>
@@ -831,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>139</v>
+        <v>268</v>
       </c>
       <c r="G10" t="n">
         <v>29.9</v>
@@ -853,38 +855,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·奇幻世界5.3动漫游戏展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>龙河路1288号 乐动力苏州湾体育中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10197</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +896,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>75</v>
+        <v>10254</v>
       </c>
       <c r="G12" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,38 +937,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>267</v>
+        <v>76</v>
       </c>
       <c r="G13" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +978,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>270</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1019,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>638</v>
+        <v>14</v>
       </c>
       <c r="G15" t="n">
-        <v>49.9</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1060,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11808</v>
+        <v>641</v>
       </c>
       <c r="G16" t="n">
-        <v>59</v>
+        <v>49.9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,33 +1106,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>12214</v>
+        <v>11840</v>
       </c>
       <c r="G17" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1142,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
+        <v>12236</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1188,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1200,19 +1202,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1229,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1241,19 +1243,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1270,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1282,19 +1284,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1306,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.05.03</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1319,23 +1321,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1352,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1364,17 +1366,58 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2024.05.03</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>35</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1550,7 +1593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1664,7 +1707,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -1705,7 +1748,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -1746,7 +1789,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>169</v>
@@ -1787,7 +1830,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -1814,7 +1857,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展（取消）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1828,10 +1871,12 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2703</v>
-      </c>
-      <c r="G7" t="n">
-        <v>68</v>
+        <v>2707</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1953,7 +1998,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>282</v>
+        <v>410</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -1965,7 +2010,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/BkAdM9dY1708409139899.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
         </is>
       </c>
     </row>
@@ -1994,7 +2039,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>139</v>
+        <v>268</v>
       </c>
       <c r="G11" t="n">
         <v>29.9</v>
@@ -2016,38 +2061,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·奇幻世界5.3动漫游戏展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>龙河路1288号 乐动力苏州湾体育中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10197</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
         </is>
       </c>
     </row>
@@ -2057,38 +2102,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>75</v>
+        <v>10254</v>
       </c>
       <c r="G13" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -2098,38 +2143,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>267</v>
+        <v>76</v>
       </c>
       <c r="G14" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -2139,38 +2184,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>270</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2180,38 +2225,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>638</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>49.9</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -2221,38 +2266,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11808</v>
+        <v>641</v>
       </c>
       <c r="G17" t="n">
-        <v>59</v>
+        <v>49.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2267,33 +2312,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>12214</v>
+        <v>11840</v>
       </c>
       <c r="G18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2303,38 +2348,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>12236</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2394,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2363,19 +2408,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2435,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2404,19 +2449,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2476,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2445,19 +2490,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2467,12 +2512,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.05.03</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2482,23 +2527,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2558,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2527,17 +2572,58 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2024.05.03</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>35</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2707</v>
+        <v>2706</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>410</v>
+        <v>737</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G10" t="n">
         <v>29.9</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10254</v>
+        <v>10293</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G14" t="n">
         <v>78</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="G16" t="n">
         <v>49.9</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11840</v>
+        <v>11862</v>
       </c>
       <c r="G17" t="n">
         <v>59</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>12236</v>
+        <v>12252</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2707</v>
+        <v>2706</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>410</v>
+        <v>737</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G11" t="n">
         <v>29.9</v>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10254</v>
+        <v>10293</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G15" t="n">
         <v>78</v>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="G17" t="n">
         <v>49.9</v>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11840</v>
+        <v>11862</v>
       </c>
       <c r="G18" t="n">
         <v>59</v>
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>12236</v>
+        <v>12252</v>
       </c>
       <c r="G19" t="n">
         <v>65</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
         <v>169</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2706</v>
+        <v>2709</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>737</v>
+        <v>1034</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G10" t="n">
         <v>29.9</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10293</v>
+        <v>10332</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -937,38 +937,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
         </is>
       </c>
     </row>
@@ -978,38 +978,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>272</v>
+        <v>76</v>
       </c>
       <c r="G14" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1019,38 +1019,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>15</v>
+        <v>273</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1060,38 +1060,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>646</v>
+        <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>49.9</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -1101,38 +1101,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11862</v>
+        <v>653</v>
       </c>
       <c r="G17" t="n">
-        <v>59</v>
+        <v>59.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1147,33 +1147,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>12252</v>
+        <v>11885</v>
       </c>
       <c r="G18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1183,38 +1183,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>12279</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1284,19 +1284,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.05.03</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1362,23 +1362,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1407,17 +1407,58 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2024.05.03</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>35</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1593,7 +1634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1707,7 +1748,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -1748,7 +1789,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -1789,7 +1830,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
         <v>169</v>
@@ -1830,7 +1871,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -1871,7 +1912,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2706</v>
+        <v>2709</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1955,7 +1996,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1998,7 +2039,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>737</v>
+        <v>1034</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2039,7 +2080,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G11" t="n">
         <v>29.9</v>
@@ -2121,7 +2162,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10293</v>
+        <v>10332</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -2143,38 +2184,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
         </is>
       </c>
     </row>
@@ -2184,38 +2225,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>272</v>
+        <v>76</v>
       </c>
       <c r="G15" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -2225,38 +2266,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>273</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2266,38 +2307,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>646</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>49.9</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -2307,38 +2348,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11862</v>
+        <v>653</v>
       </c>
       <c r="G18" t="n">
-        <v>59</v>
+        <v>59.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2353,33 +2394,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>12252</v>
+        <v>11885</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2389,38 +2430,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>27</v>
+        <v>12279</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2476,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2449,19 +2490,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2517,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2490,19 +2531,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2558,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2531,19 +2572,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2594,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024.05.03</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2568,23 +2609,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2640,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2613,17 +2654,58 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2024.05.03</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>35</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
         <v>169</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1034</v>
+        <v>1281</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G10" t="n">
-        <v>29.9</v>
+        <v>58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1007</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10332</v>
+        <v>10374</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G14" t="n">
         <v>49</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G15" t="n">
         <v>78</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>1019</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="G17" t="n">
         <v>59.9</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11885</v>
+        <v>11908</v>
       </c>
       <c r="G18" t="n">
         <v>59</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>12279</v>
+        <v>12299</v>
       </c>
       <c r="G19" t="n">
         <v>65</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
         <v>169</v>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
         <v>45</v>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1034</v>
+        <v>1281</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G11" t="n">
-        <v>29.9</v>
+        <v>58</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>1007</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10332</v>
+        <v>10374</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G15" t="n">
         <v>49</v>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G16" t="n">
         <v>78</v>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>1019</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="G18" t="n">
         <v>59.9</v>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11885</v>
+        <v>11908</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>12279</v>
+        <v>12299</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,10 +501,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.9</v>
+        <v>22</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -523,38 +525,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IwXBoz7t1708330463199.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,38 +566,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>114</v>
-      </c>
-      <c r="G4" t="n">
-        <v>30</v>
+        <v>2707</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +609,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
+          <t>苏州·国风宠物-cosplay展（取消）</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.24 19:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
-      </c>
-      <c r="G5" t="n">
-        <v>169</v>
+        <v>1166</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/BqSjvdLT1708224342995.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +652,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>1315</v>
       </c>
       <c r="G6" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IwXBoz7t1708330463199.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,40 +693,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展（取消）</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2709</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>287</v>
+      </c>
+      <c r="G7" t="n">
+        <v>58</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -730,40 +734,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展（取消）</t>
+          <t>苏州·奇幻世界5.3动漫游戏展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>龙河路1288号 乐动力苏州湾体育中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1166</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1015</v>
+      </c>
+      <c r="G8" t="n">
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
         </is>
       </c>
     </row>
@@ -773,38 +775,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1281</v>
+        <v>10435</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -814,38 +816,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>278</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
         </is>
       </c>
     </row>
@@ -855,38 +857,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·奇幻世界5.3动漫游戏展</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>龙河路1288号 乐动力苏州湾体育中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1007</v>
+        <v>79</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -896,38 +898,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10374</v>
+        <v>277</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -937,38 +939,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·X-party 国漫游戏嘉年华03</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>1024</v>
       </c>
       <c r="G13" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -978,38 +980,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>78</v>
+        <v>667</v>
       </c>
       <c r="G14" t="n">
-        <v>49</v>
+        <v>59.9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1019,38 +1021,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>275</v>
+        <v>11937</v>
       </c>
       <c r="G15" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1060,38 +1062,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1019</v>
+        <v>12336</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1101,38 +1103,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>661</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
-        <v>59.9</v>
+        <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1144,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1157,23 +1159,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11908</v>
+        <v>111</v>
       </c>
       <c r="G18" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1183,38 +1185,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>12299</v>
+        <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1231,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1243,19 +1245,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1267,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1280,23 +1282,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1308,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1321,144 +1323,21 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2024.05.02</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>27</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>71</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>36</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1548,7 +1427,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1634,7 +1513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1707,10 +1586,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39.9</v>
+        <v>22</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1729,38 +1610,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>张家港·上元节AF 汉服花灯动漫展</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>杨舍镇新农路163号 菁英羽毛球馆</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.24 09:30-02.24 17:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81508</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kd6tKAkO1706524738420.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IwXBoz7t1708330463199.jpeg</t>
         </is>
       </c>
     </row>
@@ -1770,38 +1651,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>相城大道1609号 苏州环球港</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>114</v>
-      </c>
-      <c r="G4" t="n">
-        <v>30</v>
+        <v>2707</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81565</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/JFcO48XW1706685060185.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -1811,38 +1694,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·异境次元 元宵特典 二次元派对狂欢</t>
+          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>盘门路28号 吴门印象20幢 ISZGameZone</t>
+          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.24 19:00</t>
+          <t>2024.03.03 19:30-03.03 21:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>169</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81807</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/BqSjvdLT1708224342995.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
         </is>
       </c>
     </row>
@@ -1852,38 +1735,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·国风宠物-cosplay展（取消）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
-      </c>
-      <c r="G6" t="n">
-        <v>45</v>
+        <v>1166</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IwXBoz7t1708330463199.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1778,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展（取消）</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1908,25 +1793,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2709</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1315</v>
+      </c>
+      <c r="G7" t="n">
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
         </is>
       </c>
     </row>
@@ -1936,38 +1819,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.03 19:30-03.03 21:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>287</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -1977,40 +1860,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展（取消）</t>
+          <t>苏州·奇幻世界5.3动漫游戏展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>龙河路1288号 乐动力苏州湾体育中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1166</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1015</v>
+      </c>
+      <c r="G9" t="n">
+        <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
         </is>
       </c>
     </row>
@@ -2020,38 +1901,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1281</v>
+        <v>10435</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -2061,38 +1942,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>278</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
         </is>
       </c>
     </row>
@@ -2102,38 +1983,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·奇幻世界5.3动漫游戏展</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>龙河路1288号 乐动力苏州湾体育中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1007</v>
+        <v>79</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -2143,38 +2024,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10374</v>
+        <v>277</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2184,38 +2065,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·X-party 国漫游戏嘉年华03</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>1024</v>
       </c>
       <c r="G14" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -2225,38 +2106,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>78</v>
+        <v>667</v>
       </c>
       <c r="G15" t="n">
-        <v>49</v>
+        <v>59.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2266,38 +2147,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>275</v>
+        <v>11937</v>
       </c>
       <c r="G16" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2307,38 +2188,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1019</v>
+        <v>12336</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2348,38 +2229,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>661</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
-        <v>59.9</v>
+        <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2270,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2404,23 +2285,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11908</v>
+        <v>111</v>
       </c>
       <c r="G19" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2430,38 +2311,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>12299</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2357,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2490,19 +2371,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2393,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2527,23 +2408,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2434,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2568,144 +2449,21 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2024.05.02</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>27</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>71</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>36</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,40 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.08</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>太仓·弇山夜宴</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>城厢镇县府西街40号公园弄口 弇山园</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.08 17:30-02.24 22:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>已停售</t>
-        </is>
+        <v>78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IwXBoz7t1708330463199.jpeg</t>
         </is>
       </c>
     </row>
@@ -530,12 +528,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -544,19 +542,21 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
-      </c>
-      <c r="G3" t="n">
-        <v>45</v>
+        <v>2706</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IwXBoz7t1708330463199.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,26 +566,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展（取消）</t>
+          <t>苏州·国风宠物-cosplay展（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2707</v>
+        <v>1165</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -594,12 +594,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -609,40 +609,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展（取消）</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1166</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1328</v>
+      </c>
+      <c r="G5" t="n">
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
         </is>
       </c>
     </row>
@@ -652,38 +650,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1315</v>
+        <v>289</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -693,38 +691,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·奇幻世界5.3动漫游戏展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>龙河路1288号 乐动力苏州湾体育中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>287</v>
+        <v>1017</v>
       </c>
       <c r="G7" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
         </is>
       </c>
     </row>
@@ -734,38 +732,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·奇幻世界5.3动漫游戏展</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>龙河路1288号 乐动力苏州湾体育中心</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1015</v>
+        <v>10469</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -775,38 +773,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10435</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
         </is>
       </c>
     </row>
@@ -816,38 +814,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·X-party 国漫游戏嘉年华03</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -857,38 +855,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>79</v>
+        <v>278</v>
       </c>
       <c r="G11" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -898,38 +896,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>277</v>
+        <v>1027</v>
       </c>
       <c r="G12" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -939,38 +937,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1024</v>
+        <v>673</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -980,38 +978,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>667</v>
+        <v>11959</v>
       </c>
       <c r="G14" t="n">
-        <v>59.9</v>
+        <v>59</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1026,33 +1024,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>11937</v>
+        <v>12364</v>
       </c>
       <c r="G15" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1062,38 +1060,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>12336</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1122,19 +1120,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>111</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1147,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1163,19 +1161,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1188,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1204,19 +1202,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1224,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1241,23 +1239,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1270,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1286,58 +1284,17 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>37</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1513,7 +1470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1567,40 +1524,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.08</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>太仓·弇山夜宴</t>
+          <t>太仓·龙吟动漫游戏展</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>城厢镇县府西街40号公园弄口 弇山园</t>
+          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.08 17:30-02.24 22:00</t>
+          <t>2024.02.25 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>已停售</t>
-        </is>
+        <v>78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81215</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7QA0z2031705908153925.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IwXBoz7t1708330463199.jpeg</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1570,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·第五届次元鹿角动漫游戏展（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1629,19 +1584,21 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
-      </c>
-      <c r="G3" t="n">
-        <v>45</v>
+        <v>2706</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IwXBoz7t1708330463199.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
         </is>
       </c>
     </row>
@@ -1651,40 +1608,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展（取消）</t>
+          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.03 19:30-03.03 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2707</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
         </is>
       </c>
     </row>
@@ -1694,38 +1649,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
+          <t>苏州·国风宠物-cosplay展（取消）</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.03 19:30-03.03 21:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G5" t="n">
-        <v>60</v>
+        <v>1165</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -1735,40 +1692,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展（取消）</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1166</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1328</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
         </is>
       </c>
     </row>
@@ -1778,38 +1733,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1315</v>
+        <v>289</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -1819,38 +1774,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·奇幻世界5.3动漫游戏展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>龙河路1288号 乐动力苏州湾体育中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>287</v>
+        <v>1017</v>
       </c>
       <c r="G8" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
         </is>
       </c>
     </row>
@@ -1860,38 +1815,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·奇幻世界5.3动漫游戏展</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>龙河路1288号 乐动力苏州湾体育中心</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1015</v>
+        <v>10469</v>
       </c>
       <c r="G9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -1901,38 +1856,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10435</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
         </is>
       </c>
     </row>
@@ -1942,38 +1897,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·X-party 国漫游戏嘉年华03</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="G11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1983,38 +1938,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>79</v>
+        <v>278</v>
       </c>
       <c r="G12" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -2024,38 +1979,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>277</v>
+        <v>1027</v>
       </c>
       <c r="G13" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -2065,38 +2020,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1024</v>
+        <v>673</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2106,38 +2061,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>667</v>
+        <v>11959</v>
       </c>
       <c r="G15" t="n">
-        <v>59.9</v>
+        <v>59</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2152,33 +2107,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11937</v>
+        <v>12364</v>
       </c>
       <c r="G16" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2188,38 +2143,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>12336</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2189,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2248,19 +2203,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>111</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2230,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2289,19 +2244,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2271,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2330,19 +2285,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2307,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2367,23 +2322,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2353,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2412,58 +2367,17 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>37</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·国风宠物-cosplay展（取消）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>78</v>
-      </c>
-      <c r="G2" t="n">
-        <v>55</v>
+        <v>1165</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IwXBoz7t1708330463199.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,12 +525,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展（取消）</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -538,25 +540,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2706</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1342</v>
+      </c>
+      <c r="G3" t="n">
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,40 +566,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展（取消）</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1165</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>298</v>
+      </c>
+      <c r="G4" t="n">
+        <v>58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -609,38 +607,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·奇幻世界5.3动漫游戏展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>龙河路1288号 乐动力苏州湾体育中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1328</v>
+        <v>1020</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
         </is>
       </c>
     </row>
@@ -650,38 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>289</v>
+        <v>10530</v>
       </c>
       <c r="G6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -691,38 +689,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·奇幻世界5.3动漫游戏展</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>龙河路1288号 乐动力苏州湾体育中心</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1017</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
         </is>
       </c>
     </row>
@@ -732,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10469</v>
+        <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -773,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·X-party 国漫游戏嘉年华03</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>282</v>
       </c>
       <c r="G9" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -814,38 +812,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>79</v>
+        <v>1030</v>
       </c>
       <c r="G10" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -855,38 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>278</v>
+        <v>683</v>
       </c>
       <c r="G11" t="n">
-        <v>78</v>
+        <v>59.9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -896,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1027</v>
+        <v>11989</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -937,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>673</v>
+        <v>12404</v>
       </c>
       <c r="G13" t="n">
-        <v>59.9</v>
+        <v>65</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -978,12 +976,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -993,23 +991,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>11959</v>
+        <v>30</v>
       </c>
       <c r="G14" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1019,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12364</v>
+        <v>114</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1063,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1079,19 +1077,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1104,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1120,19 +1118,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1140,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1157,23 +1155,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1181,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1198,103 +1196,21 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>72</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>39</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1384,7 +1300,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1470,7 +1386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1524,38 +1440,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>太仓·龙吟动漫游戏展</t>
+          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>滨河路128号 凯景世纪大酒店(太仓滨河路店)</t>
+          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.03 19:30-03.03 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>78</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81242</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IwXBoz7t1708330463199.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
         </is>
       </c>
     </row>
@@ -1565,26 +1481,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>苏州·第五届次元鹿角动漫游戏展（取消）</t>
+          <t>苏州·国风宠物-cosplay展（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.25 10:00-02.25 17:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2706</v>
+        <v>1165</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1593,12 +1509,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79333</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tqrMA6qB1704787264871.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -1608,38 +1524,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.03 19:30-03.03 21:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>1342</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
         </is>
       </c>
     </row>
@@ -1649,40 +1565,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展（取消）</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1165</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>298</v>
+      </c>
+      <c r="G5" t="n">
+        <v>58</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
         </is>
       </c>
     </row>
@@ -1692,38 +1606,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·奇幻世界5.3动漫游戏展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>龙河路1288号 乐动力苏州湾体育中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1328</v>
+        <v>1020</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
         </is>
       </c>
     </row>
@@ -1733,38 +1647,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>289</v>
+        <v>10530</v>
       </c>
       <c r="G7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -1774,38 +1688,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·奇幻世界5.3动漫游戏展</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>龙河路1288号 乐动力苏州湾体育中心</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1017</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
         </is>
       </c>
     </row>
@@ -1815,38 +1729,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10469</v>
+        <v>80</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1856,38 +1770,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·X-party 国漫游戏嘉年华03</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>282</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1897,38 +1811,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>79</v>
+        <v>1030</v>
       </c>
       <c r="G11" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -1938,38 +1852,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>278</v>
+        <v>683</v>
       </c>
       <c r="G12" t="n">
-        <v>78</v>
+        <v>59.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1979,38 +1893,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1027</v>
+        <v>11989</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2020,38 +1934,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>673</v>
+        <v>12404</v>
       </c>
       <c r="G14" t="n">
-        <v>59.9</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2061,12 +1975,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2076,23 +1990,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>11959</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2102,38 +2016,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>12364</v>
+        <v>114</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2062,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2162,19 +2076,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2103,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2203,19 +2117,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2139,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2240,23 +2154,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -2266,12 +2180,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2281,103 +2195,21 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>72</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2024.05.03</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>39</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1342</v>
+        <v>1350</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10530</v>
+        <v>10580</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G9" t="n">
         <v>78</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="G11" t="n">
         <v>59.9</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>11989</v>
+        <v>12006</v>
       </c>
       <c r="G12" t="n">
         <v>59</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12404</v>
+        <v>12423</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1342</v>
+        <v>1350</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10530</v>
+        <v>10580</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G10" t="n">
         <v>78</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="G12" t="n">
         <v>59.9</v>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>11989</v>
+        <v>12006</v>
       </c>
       <c r="G13" t="n">
         <v>59</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12404</v>
+        <v>12423</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,38 +525,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·OrangeOrange新春随舞派对【免费展会】</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>狮山路298号 金鹰国际购物中心(狮山路店)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.16 13:00-03.16 17:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1350</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82046</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/0OH3Ax4I1708913393518.png</t>
         </is>
       </c>
     </row>
@@ -566,38 +566,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>302</v>
+        <v>1365</v>
       </c>
       <c r="G4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
         </is>
       </c>
     </row>
@@ -607,38 +607,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·奇幻世界5.3动漫游戏展</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>龙河路1288号 乐动力苏州湾体育中心</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1024</v>
+        <v>306</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>52.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/CP95X8ao1708934930351.jpeg</t>
         </is>
       </c>
     </row>
@@ -648,38 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·奇幻世界5.3动漫游戏展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>龙河路1288号 乐动力苏州湾体育中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10580</v>
+        <v>1030</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
         </is>
       </c>
     </row>
@@ -689,38 +689,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·X-party 国漫游戏嘉年华03</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>10636</v>
       </c>
       <c r="G7" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -730,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="G9" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -812,38 +812,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1031</v>
+        <v>288</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,38 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>688</v>
+        <v>1033</v>
       </c>
       <c r="G11" t="n">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>12006</v>
+        <v>698</v>
       </c>
       <c r="G12" t="n">
-        <v>59</v>
+        <v>59.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -940,33 +940,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12423</v>
+        <v>12028</v>
       </c>
       <c r="G13" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>12455</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1036,19 +1036,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.05.03</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1155,23 +1155,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1200,17 +1200,58 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2024.05.03</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>42</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
@@ -1386,7 +1427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1524,38 +1565,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·OrangeOrange新春随舞派对【免费展会】</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>狮山路298号 金鹰国际购物中心(狮山路店)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.16 13:00-03.16 17:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1350</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82046</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/0OH3Ax4I1708913393518.png</t>
         </is>
       </c>
     </row>
@@ -1565,38 +1606,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>302</v>
+        <v>1365</v>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZYkvUFn41706869061984.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
         </is>
       </c>
     </row>
@@ -1606,38 +1647,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·奇幻世界5.3动漫游戏展</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>龙河路1288号 乐动力苏州湾体育中心</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1024</v>
+        <v>306</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>52.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/CP95X8ao1708934930351.jpeg</t>
         </is>
       </c>
     </row>
@@ -1647,38 +1688,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·奇幻世界5.3动漫游戏展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>龙河路1288号 乐动力苏州湾体育中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10580</v>
+        <v>1030</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
         </is>
       </c>
     </row>
@@ -1688,38 +1729,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·X-party 国漫游戏嘉年华03</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>10636</v>
       </c>
       <c r="G8" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -1729,38 +1770,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
         </is>
       </c>
     </row>
@@ -1770,38 +1811,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="G10" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1811,38 +1852,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1031</v>
+        <v>288</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1852,38 +1893,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>688</v>
+        <v>1033</v>
       </c>
       <c r="G12" t="n">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -1893,38 +1934,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12006</v>
+        <v>698</v>
       </c>
       <c r="G13" t="n">
-        <v>59</v>
+        <v>59.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1939,33 +1980,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12423</v>
+        <v>12028</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1975,38 +2016,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>12455</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2062,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2035,19 +2076,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2103,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2076,19 +2117,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2144,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2117,19 +2158,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2139,12 +2180,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.05.03</t>
+          <t>2024.05.02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2154,23 +2195,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2226,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2199,17 +2240,58 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024.05.03</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>42</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1365</v>
+        <v>1374</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G5" t="n">
         <v>52.2</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10636</v>
+        <v>10669</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
         <v>48</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G10" t="n">
         <v>78</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="G12" t="n">
         <v>59.9</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12028</v>
+        <v>12040</v>
       </c>
       <c r="G13" t="n">
         <v>59</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12455</v>
+        <v>12482</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1365</v>
+        <v>1374</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G6" t="n">
         <v>52.2</v>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10636</v>
+        <v>10669</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G11" t="n">
         <v>78</v>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="G13" t="n">
         <v>59.9</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12028</v>
+        <v>12040</v>
       </c>
       <c r="G14" t="n">
         <v>59</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12455</v>
+        <v>12482</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1374</v>
+        <v>1395</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="G5" t="n">
         <v>52.2</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10669</v>
+        <v>10730</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G8" t="n">
         <v>48</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G10" t="n">
         <v>78</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>701</v>
+        <v>715</v>
       </c>
       <c r="G12" t="n">
         <v>59.9</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12040</v>
+        <v>12061</v>
       </c>
       <c r="G13" t="n">
         <v>59</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12482</v>
+        <v>12513</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1374</v>
+        <v>1395</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="G6" t="n">
         <v>52.2</v>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10669</v>
+        <v>10730</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G11" t="n">
         <v>78</v>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>701</v>
+        <v>715</v>
       </c>
       <c r="G13" t="n">
         <v>59.9</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12040</v>
+        <v>12061</v>
       </c>
       <c r="G14" t="n">
         <v>59</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12482</v>
+        <v>12513</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1395</v>
+        <v>1407</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G5" t="n">
         <v>52.2</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10730</v>
+        <v>10765</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
         <v>48</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G10" t="n">
         <v>78</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="G12" t="n">
         <v>59.9</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12061</v>
+        <v>12084</v>
       </c>
       <c r="G13" t="n">
         <v>59</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12513</v>
+        <v>12544</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1395</v>
+        <v>1407</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G6" t="n">
         <v>52.2</v>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10730</v>
+        <v>10765</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G11" t="n">
         <v>78</v>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="G13" t="n">
         <v>59.9</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12061</v>
+        <v>12084</v>
       </c>
       <c r="G14" t="n">
         <v>59</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12513</v>
+        <v>12544</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1407</v>
+        <v>1432</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G5" t="n">
         <v>52.2</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10765</v>
+        <v>10797</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="G12" t="n">
-        <v>59.9</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12084</v>
+        <v>12110</v>
       </c>
       <c r="G13" t="n">
         <v>59</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12544</v>
+        <v>12573</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1407</v>
+        <v>1432</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G6" t="n">
         <v>52.2</v>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10765</v>
+        <v>10797</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="G13" t="n">
-        <v>59.9</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12084</v>
+        <v>12110</v>
       </c>
       <c r="G14" t="n">
         <v>59</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12544</v>
+        <v>12573</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1432</v>
+        <v>1443</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="G5" t="n">
         <v>52.2</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10797</v>
+        <v>10819</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
         <v>48</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G10" t="n">
         <v>78</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="G12" t="n">
         <v>69.90000000000001</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12110</v>
+        <v>12137</v>
       </c>
       <c r="G13" t="n">
         <v>59</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12573</v>
+        <v>12597</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1432</v>
+        <v>1443</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="G6" t="n">
         <v>52.2</v>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10797</v>
+        <v>10819</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G11" t="n">
         <v>78</v>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="G13" t="n">
         <v>69.90000000000001</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12110</v>
+        <v>12137</v>
       </c>
       <c r="G14" t="n">
         <v>59</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12573</v>
+        <v>12597</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1443</v>
+        <v>1455</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G5" t="n">
         <v>52.2</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10819</v>
+        <v>10857</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -730,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·X-party 国漫游戏嘉年华03</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="G8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
         </is>
       </c>
     </row>
@@ -831,10 +831,12 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>300</v>
-      </c>
-      <c r="G10" t="n">
-        <v>78</v>
+        <v>303</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -872,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="G12" t="n">
         <v>69.90000000000001</v>
@@ -954,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12137</v>
+        <v>12155</v>
       </c>
       <c r="G13" t="n">
         <v>59</v>
@@ -995,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12597</v>
+        <v>12629</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1159,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1341,7 +1343,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1500,7 +1502,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1541,7 +1543,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1584,7 +1586,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
@@ -1625,7 +1627,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1443</v>
+        <v>1455</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1666,7 +1668,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G6" t="n">
         <v>52.2</v>
@@ -1707,7 +1709,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1748,7 +1750,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10819</v>
+        <v>10857</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1770,38 +1772,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·X-party 国漫游戏嘉年华03</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="G9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1811,38 +1813,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="G10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
         </is>
       </c>
     </row>
@@ -1871,10 +1873,12 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>300</v>
-      </c>
-      <c r="G11" t="n">
-        <v>78</v>
+        <v>303</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1912,7 +1916,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1953,7 +1957,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="G13" t="n">
         <v>69.90000000000001</v>
@@ -1994,7 +1998,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12137</v>
+        <v>12155</v>
       </c>
       <c r="G14" t="n">
         <v>59</v>
@@ -2035,7 +2039,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12597</v>
+        <v>12629</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2199,7 +2203,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
@@ -566,7 +566,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1455</v>
+        <v>1464</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -607,7 +607,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="G5" t="n">
         <v>52.2</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -689,7 +689,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10857</v>
+        <v>10900</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -730,7 +730,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -831,11 +831,11 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>已停售</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="G12" t="n">
         <v>69.90000000000001</v>
@@ -937,7 +937,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12155</v>
+        <v>12168</v>
       </c>
       <c r="G13" t="n">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12629</v>
+        <v>12653</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.05.03</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.05.03</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1429,7 +1429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1455</v>
+        <v>1464</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="G6" t="n">
         <v>52.2</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10857</v>
+        <v>10900</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1772,38 +1772,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>85</v>
+        <v>10900</v>
       </c>
       <c r="G9" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -1813,38 +1813,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·X-party 国漫游戏嘉年华03</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1854,40 +1854,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>303</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>已停售</t>
-        </is>
+        <v>29</v>
+      </c>
+      <c r="G11" t="n">
+        <v>48</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
         </is>
       </c>
     </row>
@@ -1897,38 +1895,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1054</v>
-      </c>
-      <c r="G12" t="n">
-        <v>60</v>
+        <v>301</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
         </is>
       </c>
     </row>
@@ -1938,38 +1938,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>732</v>
+        <v>1054</v>
       </c>
       <c r="G13" t="n">
-        <v>69.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -1979,38 +1979,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12155</v>
+        <v>737</v>
       </c>
       <c r="G14" t="n">
-        <v>59</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2020,38 +2020,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12629</v>
+        <v>12168</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2061,38 +2061,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>12653</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2121,19 +2121,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2143,12 +2143,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2162,19 +2162,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2184,12 +2184,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.05.02</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2203,19 +2203,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.05.03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2240,23 +2240,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.05.03</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2285,17 +2285,58 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>43</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1464</v>
+        <v>1475</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>366</v>
+        <v>470</v>
       </c>
       <c r="G5" t="n">
         <v>52.2</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10900</v>
+        <v>10948</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -730,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>85</v>
+        <v>10948</v>
       </c>
       <c r="G8" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·X-party 国漫游戏嘉年华03</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="G9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -817,35 +817,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>301</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="G10" t="n">
+        <v>48</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202403/GWNvc78z1709275224442.jpeg</t>
         </is>
       </c>
     </row>
@@ -855,38 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1054</v>
+        <v>306</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202403/nIPoXWqO1709275656198.jpeg</t>
         </is>
       </c>
     </row>
@@ -896,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>737</v>
+        <v>1056</v>
       </c>
       <c r="G12" t="n">
-        <v>69.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -937,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12168</v>
+        <v>741</v>
       </c>
       <c r="G13" t="n">
-        <v>160</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -983,33 +981,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12653</v>
+        <v>12182</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -1019,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>12683</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1063,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1079,19 +1077,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1104,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1120,19 +1118,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1145,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1161,19 +1159,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1181,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1198,23 +1196,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1227,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1243,19 +1241,101 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2024.05.03 14:00-05.03 16:00</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>43</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>【会员购严选】苏州·Come in joy动漫国潮文化节</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>金山南路288号 广电国际会展中心</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2024.06.08 10:00-06.09 17:00</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>60</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=82233</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202403/F86lgbSt1709278264141.jpeg</t>
         </is>
       </c>
     </row>
@@ -1343,10 +1423,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G2" t="n">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1429,7 +1511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1502,10 +1584,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G2" t="n">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1586,7 +1670,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
@@ -1627,7 +1711,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1464</v>
+        <v>1475</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1668,7 +1752,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>366</v>
+        <v>470</v>
       </c>
       <c r="G6" t="n">
         <v>52.2</v>
@@ -1709,7 +1793,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1750,7 +1834,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10900</v>
+        <v>10948</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1791,7 +1875,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10900</v>
+        <v>10948</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1873,7 +1957,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G11" t="n">
         <v>48</v>
@@ -1885,7 +1969,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/WaQk4nUt1708679999084.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202403/GWNvc78z1709275224442.jpeg</t>
         </is>
       </c>
     </row>
@@ -1914,12 +1998,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>301</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>306</v>
+      </c>
+      <c r="G12" t="n">
+        <v>88</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1928,7 +2010,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SjKfDxBh1705041298410.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202403/nIPoXWqO1709275656198.jpeg</t>
         </is>
       </c>
     </row>
@@ -1957,7 +2039,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -1998,7 +2080,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="G14" t="n">
         <v>69.90000000000001</v>
@@ -2039,10 +2121,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12168</v>
+        <v>12182</v>
       </c>
       <c r="G15" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2080,7 +2162,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>12653</v>
+        <v>12683</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -2162,7 +2244,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -2244,7 +2326,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -2339,6 +2421,47 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>【会员购严选】苏州·Come in joy动漫国潮文化节</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>金山南路288号 广电国际会展中心</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2024.06.08 10:00-06.09 17:00</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>60</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=82233</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202403/F86lgbSt1709278264141.jpeg</t>
         </is>
       </c>
     </row>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>470</v>
+        <v>574</v>
       </c>
       <c r="G5" t="n">
         <v>52.2</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10948</v>
+        <v>10979</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10948</v>
+        <v>10979</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G11" t="n">
         <v>88</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="G13" t="n">
         <v>69.90000000000001</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12182</v>
+        <v>12197</v>
       </c>
       <c r="G14" t="n">
         <v>75</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12683</v>
+        <v>12708</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>470</v>
+        <v>574</v>
       </c>
       <c r="G6" t="n">
         <v>52.2</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10948</v>
+        <v>10979</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10948</v>
+        <v>10979</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G12" t="n">
         <v>88</v>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="G14" t="n">
         <v>69.90000000000001</v>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12182</v>
+        <v>12197</v>
       </c>
       <c r="G15" t="n">
         <v>75</v>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>12683</v>
+        <v>12708</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1480</v>
+        <v>1500</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G5" t="n">
         <v>52.2</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10979</v>
+        <v>11046</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10979</v>
+        <v>11046</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="G11" t="n">
         <v>88</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="G13" t="n">
         <v>69.90000000000001</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12197</v>
+        <v>12221</v>
       </c>
       <c r="G14" t="n">
         <v>75</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12708</v>
+        <v>12752</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1480</v>
+        <v>1500</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G6" t="n">
         <v>52.2</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10979</v>
+        <v>11046</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10979</v>
+        <v>11046</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="G12" t="n">
         <v>88</v>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="G14" t="n">
         <v>69.90000000000001</v>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12197</v>
+        <v>12221</v>
       </c>
       <c r="G15" t="n">
         <v>75</v>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>12708</v>
+        <v>12752</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G5" t="n">
         <v>52.2</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11046</v>
+        <v>11080</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -730,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11046</v>
+        <v>85</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202403/GWNvc78z1709275224442.jpeg</t>
         </is>
       </c>
     </row>
@@ -817,33 +817,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·X-party 国漫游戏嘉年华03</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>321</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202403/GWNvc78z1709275224442.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202403/nIPoXWqO1709275656198.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,38 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>319</v>
+        <v>1067</v>
       </c>
       <c r="G11" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202403/nIPoXWqO1709275656198.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1064</v>
+        <v>759</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>751</v>
+        <v>12231</v>
       </c>
       <c r="G13" t="n">
-        <v>69.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -981,33 +981,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12221</v>
+        <v>12776</v>
       </c>
       <c r="G14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12752</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1196,23 +1196,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,77 +1263,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>【会员购严选】苏州·Come in joy动漫国潮文化节</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.06.08 10:00-06.09 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82233</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>【会员购严选】苏州·Come in joy动漫国潮文化节</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>金山南路288号 广电国际会展中心</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2024.06.08 10:00-06.09 17:00</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>37</v>
-      </c>
-      <c r="G22" t="n">
-        <v>60</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82233</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202403/F86lgbSt1709278264141.jpeg</t>
         </is>
@@ -1511,7 +1470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1670,7 +1629,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
@@ -1711,7 +1670,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1752,7 +1711,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G6" t="n">
         <v>52.2</v>
@@ -1793,7 +1752,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1834,7 +1793,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11046</v>
+        <v>11080</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1856,38 +1815,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>11046</v>
+        <v>85</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1897,38 +1856,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202403/GWNvc78z1709275224442.jpeg</t>
         </is>
       </c>
     </row>
@@ -1943,33 +1902,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·X-party 国漫游戏嘉年华03</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>321</v>
       </c>
       <c r="G11" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202403/GWNvc78z1709275224442.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202403/nIPoXWqO1709275656198.jpeg</t>
         </is>
       </c>
     </row>
@@ -1979,38 +1938,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>319</v>
+        <v>1067</v>
       </c>
       <c r="G12" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202403/nIPoXWqO1709275656198.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -2020,38 +1979,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1064</v>
+        <v>759</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -2061,38 +2020,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>751</v>
+        <v>12231</v>
       </c>
       <c r="G14" t="n">
-        <v>69.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2107,33 +2066,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12221</v>
+        <v>12776</v>
       </c>
       <c r="G15" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2143,38 +2102,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>12752</v>
+        <v>32</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2148,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2203,19 +2162,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2189,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2244,19 +2203,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2230,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2285,19 +2244,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2307,12 +2266,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2322,23 +2281,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2312,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2367,19 +2326,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
       </c>
     </row>
@@ -2389,77 +2348,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>【会员购严选】苏州·Come in joy动漫国潮文化节</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.06.08 10:00-06.09 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>43</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82233</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>【会员购严选】苏州·Come in joy动漫国潮文化节</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>金山南路288号 广电国际会展中心</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2024.06.08 10:00-06.09 17:00</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>37</v>
-      </c>
-      <c r="G23" t="n">
-        <v>60</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82233</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202403/F86lgbSt1709278264141.jpeg</t>
         </is>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1510</v>
+        <v>1519</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="G5" t="n">
         <v>52.2</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11080</v>
+        <v>11144</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G8" t="n">
         <v>49</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G10" t="n">
         <v>88</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="G12" t="n">
         <v>69.90000000000001</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12231</v>
+        <v>12254</v>
       </c>
       <c r="G13" t="n">
         <v>75</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12776</v>
+        <v>12831</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1510</v>
+        <v>1519</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="G6" t="n">
         <v>52.2</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11080</v>
+        <v>11144</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G11" t="n">
         <v>88</v>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="G13" t="n">
         <v>69.90000000000001</v>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12231</v>
+        <v>12254</v>
       </c>
       <c r="G14" t="n">
         <v>75</v>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12776</v>
+        <v>12831</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>

--- a/苏州-漫展信息.xlsx
+++ b/苏州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1519</v>
+        <v>1531</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G5" t="n">
         <v>52.2</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11144</v>
+        <v>11181</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G8" t="n">
         <v>49</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G10" t="n">
         <v>88</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="G12" t="n">
         <v>69.90000000000001</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12254</v>
+        <v>12263</v>
       </c>
       <c r="G13" t="n">
         <v>75</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12831</v>
+        <v>12856</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1309,7 +1309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1354,49 +1354,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Cover</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2024.03.03 19:30-03.03 21:00</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>13</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1524,26 +1481,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>苏州·龙猫和他的朋友·动漫作品音乐会</t>
+          <t>苏州·国风宠物-cosplay展（取消）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>星湖街555号高教区(体育馆南侧) 苏州独墅湖影剧院</t>
+          <t>金山南路影视城 木渎影视城会展中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.03.03 19:30-03.03 21:00</t>
+          <t>2024.03.08 09:00-03.10 17:30</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>1165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1552,12 +1509,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/gqnOEjvJ1707214629948.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
         </is>
       </c>
     </row>
@@ -1567,40 +1524,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>苏州·国风宠物-cosplay展（取消）</t>
+          <t>苏州·OrangeOrange新春随舞派对【免费展会】</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金山南路影视城 木渎影视城会展中心</t>
+          <t>狮山路298号 金鹰国际购物中心(狮山路店)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.03.08 09:00-03.10 17:30</t>
+          <t>2024.03.16 13:00-03.16 17:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1166</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>89</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80635</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82046</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Rfd9PcBN1704781416369.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/0OH3Ax4I1708913393518.png</t>
         </is>
       </c>
     </row>
@@ -1610,38 +1565,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>苏州·OrangeOrange新春随舞派对【免费展会】</t>
+          <t>苏州·世纪幻想动漫游戏展2.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>狮山路298号 金鹰国际购物中心(狮山路店)</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.16 13:00-03.16 17:30</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84</v>
+        <v>1531</v>
       </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/0OH3Ax4I1708913393518.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
         </is>
       </c>
     </row>
@@ -1651,38 +1606,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>苏州·世纪幻想动漫游戏展2.0</t>
+          <t>苏州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1519</v>
+        <v>585</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>52.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81387</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/isVyI9hH1708590817616.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/CP95X8ao1708934930351.jpeg</t>
         </is>
       </c>
     </row>
@@ -1692,38 +1647,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>苏州·Look Look动漫嘉年华</t>
+          <t>苏州·奇幻世界5.3动漫游戏展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>阳澄半岛慈云路168号(重元寺北) 阳澄湖澜廷度假酒店</t>
+          <t>龙河路1288号 乐动力苏州湾体育中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:30</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>583</v>
+        <v>1077</v>
       </c>
       <c r="G6" t="n">
-        <v>52.2</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81698</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/CP95X8ao1708934930351.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
         </is>
       </c>
     </row>
@@ -1733,38 +1688,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>苏州·奇幻世界5.3动漫游戏展</t>
+          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>龙河路1288号 乐动力苏州湾体育中心</t>
+          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1075</v>
+        <v>11181</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82002</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/HlxVHAz91708593664222.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
         </is>
       </c>
     </row>
@@ -1774,38 +1729,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>【会员购严选】苏州·Anime LIVE 国际动漫品牌博览会</t>
+          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金山南路288号木渎影视城F2 苏州广电国际会展中心</t>
+          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 16:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11144</v>
+        <v>85</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81827</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/6oSFbWOx1707301464970.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
         </is>
       </c>
     </row>
@@ -1815,38 +1770,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州·第一届寒假动漫展宅舞比赛-CF01</t>
+          <t>苏州·X-party 国漫游戏嘉年华03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>润元路润南巷172号,地铁二号线陆慕站东200米,近市旅游换乘中心北100米 斐利酒店</t>
+          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 16:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80528</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/oWbVnOjD1704445446390.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202403/GWNvc78z1709275224442.jpeg</t>
         </is>
       </c>
     </row>
@@ -1861,33 +1816,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>苏州·X-party 国漫游戏嘉年华03</t>
+          <t>苏州·绘时国乙1.0-秩序之外</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>秋枫街与开平路交叉口西南角 爱琴海购物中心</t>
+          <t>石路步行街永福桥浜15号 银河广场</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.13 13:30-04.13 20:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>330</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82042</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202403/GWNvc78z1709275224442.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202403/nIPoXWqO1709275656198.jpeg</t>
         </is>
       </c>
     </row>
@@ -1897,38 +1852,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>苏州·绘时国乙1.0-秩序之外</t>
+          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>石路步行街永福桥浜15号 银河广场</t>
+          <t>清禾路886号 尹山湖大剧院</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.04.13 13:30-04.13 20:00</t>
+          <t>2024.04.20 10:00-04.20 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>325</v>
+        <v>1073</v>
       </c>
       <c r="G11" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202403/nIPoXWqO1709275656198.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
         </is>
       </c>
     </row>
@@ -1938,38 +1893,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>苏州·首届Redamancy动漫游戏嘉年华</t>
+          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>清禾路886号 尹山湖大剧院</t>
+          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.20 17:00</t>
+          <t>2024.04.21 10:00-04.21 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1071</v>
+        <v>769</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81879</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/lR4oJWzI1708309129629.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
         </is>
       </c>
     </row>
@@ -1979,38 +1934,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>苏州·梦幻岛 国乙主题文化展（日夜场） 梦幻岛之约3.0</t>
+          <t>昆山·第十二届理想乡动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>清禾路888号2号楼3楼 格莱美婚礼宴会中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.04.21 10:00-04.21 21:00</t>
+          <t>2024.05.01 10:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>762</v>
+        <v>12263</v>
       </c>
       <c r="G13" t="n">
-        <v>69.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/X0PZ3YhH1703822037665.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
         </is>
       </c>
     </row>
@@ -2025,33 +1980,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展</t>
+          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.03 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12254</v>
+        <v>12856</v>
       </c>
       <c r="G14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/9xMTQMlg1696736126094.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
         </is>
       </c>
     </row>
@@ -2061,38 +2016,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>苏州·第十七届 I COME ACG  动漫品牌博览会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>金山南路288号 广电国际会展中心</t>
+          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.02 14:00-05.02 16:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12831</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79789</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/lau3mW031702535438289.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2062,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾北齐后主签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2121,19 +2076,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81116</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/EubrAneC1705648695005.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2103,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾啊川签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2162,19 +2117,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81100</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/F24i5GMX1705646667852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2144,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾漠小然签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2203,19 +2158,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81119</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/SDnLB1gR1705648838683.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2180,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾葫芦岛老八签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2240,23 +2195,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.05.02 14:00-05.02 16:00</t>
+          <t>2024.05.03 14:00-05.03 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81118</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/uHOCneLv1705648779163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2226,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾沈辞签售会</t>
+          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2285,19 +2240,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81120</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Pay1rR61705648901961.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
         </is>
       </c>
     </row>
@@ -2307,77 +2262,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>昆山·第十二届理想乡动漫游戏展嘉宾矮乐多aliga签售会</t>
+          <t>【会员购严选】苏州·Come in joy动漫国潮文化节</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>花桥经济开发区绿地大道1598号 花桥国际博览中心</t>
+          <t>金山南路288号 广电国际会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.05.03 14:00-05.03 16:00</t>
+          <t>2024.06.08 10:00-06.09 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81114</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=82233</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Peub7FOc1705648580577.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>【会员购严选】苏州·Come in joy动漫国潮文化节</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>金山南路288号 广电国际会展中心</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2024.06.08 10:00-06.09 17:00</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>51</v>
-      </c>
-      <c r="G22" t="n">
-        <v>60</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=82233</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202403/F86lgbSt1709278264141.jpeg</t>
         </is>
